--- a/docs/testbook/第xx小组_垃圾自动识别分类系统_测试成绩书.xlsx
+++ b/docs/testbook/第xx小组_垃圾自动识别分类系统_测试成绩书.xlsx
@@ -2878,7 +2878,7 @@
     </row>
     <row r="18" ht="18" customHeight="1" s="92">
       <c r="A18" s="3" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="B18" s="70" t="n"/>
       <c r="C18" s="70" t="n"/>
@@ -3205,7 +3205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG89"/>
+  <dimension ref="A1:BG113"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.6328125" defaultRowHeight="12"/>
   <cols>
     <col width="2.6328125" customWidth="1" style="13" min="1" max="20"/>
@@ -3572,7 +3572,7 @@
       <c r="AO5" s="93" t="n"/>
       <c r="AP5" s="94" t="n"/>
       <c r="AQ5" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR5" s="93" t="n"/>
       <c r="AS5" s="93" t="n"/>
@@ -3654,7 +3654,7 @@
       <c r="AO6" s="93" t="n"/>
       <c r="AP6" s="94" t="n"/>
       <c r="AQ6" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR6" s="93" t="n"/>
       <c r="AS6" s="93" t="n"/>
@@ -3735,7 +3735,7 @@
       <c r="AO7" s="93" t="n"/>
       <c r="AP7" s="94" t="n"/>
       <c r="AQ7" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR7" s="93" t="n"/>
       <c r="AS7" s="93" t="n"/>
@@ -3816,7 +3816,7 @@
       <c r="AO8" s="93" t="n"/>
       <c r="AP8" s="94" t="n"/>
       <c r="AQ8" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR8" s="93" t="n"/>
       <c r="AS8" s="93" t="n"/>
@@ -3898,7 +3898,7 @@
       <c r="AO9" s="93" t="n"/>
       <c r="AP9" s="94" t="n"/>
       <c r="AQ9" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR9" s="93" t="n"/>
       <c r="AS9" s="93" t="n"/>
@@ -3980,7 +3980,7 @@
       <c r="AO10" s="93" t="n"/>
       <c r="AP10" s="94" t="n"/>
       <c r="AQ10" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR10" s="93" t="n"/>
       <c r="AS10" s="93" t="n"/>
@@ -4062,7 +4062,7 @@
       <c r="AO11" s="93" t="n"/>
       <c r="AP11" s="94" t="n"/>
       <c r="AQ11" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR11" s="93" t="n"/>
       <c r="AS11" s="93" t="n"/>
@@ -4144,7 +4144,7 @@
       <c r="AO12" s="93" t="n"/>
       <c r="AP12" s="94" t="n"/>
       <c r="AQ12" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR12" s="93" t="n"/>
       <c r="AS12" s="93" t="n"/>
@@ -4226,7 +4226,7 @@
       <c r="AO13" s="93" t="n"/>
       <c r="AP13" s="94" t="n"/>
       <c r="AQ13" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR13" s="93" t="n"/>
       <c r="AS13" s="93" t="n"/>
@@ -4308,7 +4308,7 @@
       <c r="AO14" s="93" t="n"/>
       <c r="AP14" s="94" t="n"/>
       <c r="AQ14" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR14" s="93" t="n"/>
       <c r="AS14" s="93" t="n"/>
@@ -4390,7 +4390,7 @@
       <c r="AO15" s="93" t="n"/>
       <c r="AP15" s="94" t="n"/>
       <c r="AQ15" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR15" s="93" t="n"/>
       <c r="AS15" s="93" t="n"/>
@@ -4472,7 +4472,7 @@
       <c r="AO16" s="93" t="n"/>
       <c r="AP16" s="94" t="n"/>
       <c r="AQ16" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR16" s="93" t="n"/>
       <c r="AS16" s="93" t="n"/>
@@ -4555,7 +4555,7 @@
       <c r="AO17" s="93" t="n"/>
       <c r="AP17" s="94" t="n"/>
       <c r="AQ17" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR17" s="93" t="n"/>
       <c r="AS17" s="93" t="n"/>
@@ -4636,7 +4636,7 @@
       <c r="AO18" s="93" t="n"/>
       <c r="AP18" s="94" t="n"/>
       <c r="AQ18" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR18" s="93" t="n"/>
       <c r="AS18" s="93" t="n"/>
@@ -4717,7 +4717,7 @@
       <c r="AO19" s="93" t="n"/>
       <c r="AP19" s="94" t="n"/>
       <c r="AQ19" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR19" s="93" t="n"/>
       <c r="AS19" s="93" t="n"/>
@@ -4798,7 +4798,7 @@
       <c r="AO20" s="93" t="n"/>
       <c r="AP20" s="94" t="n"/>
       <c r="AQ20" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR20" s="93" t="n"/>
       <c r="AS20" s="93" t="n"/>
@@ -4880,7 +4880,7 @@
       <c r="AO21" s="93" t="n"/>
       <c r="AP21" s="94" t="n"/>
       <c r="AQ21" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR21" s="93" t="n"/>
       <c r="AS21" s="93" t="n"/>
@@ -4962,7 +4962,7 @@
       <c r="AO22" s="93" t="n"/>
       <c r="AP22" s="94" t="n"/>
       <c r="AQ22" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR22" s="93" t="n"/>
       <c r="AS22" s="93" t="n"/>
@@ -5044,7 +5044,7 @@
       <c r="AO23" s="93" t="n"/>
       <c r="AP23" s="94" t="n"/>
       <c r="AQ23" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR23" s="93" t="n"/>
       <c r="AS23" s="93" t="n"/>
@@ -5126,7 +5126,7 @@
       <c r="AO24" s="93" t="n"/>
       <c r="AP24" s="94" t="n"/>
       <c r="AQ24" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR24" s="93" t="n"/>
       <c r="AS24" s="93" t="n"/>
@@ -5208,7 +5208,7 @@
       <c r="AO25" s="93" t="n"/>
       <c r="AP25" s="94" t="n"/>
       <c r="AQ25" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR25" s="93" t="n"/>
       <c r="AS25" s="93" t="n"/>
@@ -5289,7 +5289,7 @@
       <c r="AO26" s="93" t="n"/>
       <c r="AP26" s="94" t="n"/>
       <c r="AQ26" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR26" s="93" t="n"/>
       <c r="AS26" s="93" t="n"/>
@@ -5370,7 +5370,7 @@
       <c r="AO27" s="93" t="n"/>
       <c r="AP27" s="94" t="n"/>
       <c r="AQ27" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR27" s="93" t="n"/>
       <c r="AS27" s="93" t="n"/>
@@ -5452,7 +5452,7 @@
       <c r="AO28" s="93" t="n"/>
       <c r="AP28" s="94" t="n"/>
       <c r="AQ28" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR28" s="93" t="n"/>
       <c r="AS28" s="93" t="n"/>
@@ -5535,7 +5535,7 @@
       <c r="AO29" s="93" t="n"/>
       <c r="AP29" s="94" t="n"/>
       <c r="AQ29" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR29" s="93" t="n"/>
       <c r="AS29" s="93" t="n"/>
@@ -5617,7 +5617,7 @@
       <c r="AO30" s="93" t="n"/>
       <c r="AP30" s="94" t="n"/>
       <c r="AQ30" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR30" s="93" t="n"/>
       <c r="AS30" s="93" t="n"/>
@@ -5699,7 +5699,7 @@
       <c r="AO31" s="93" t="n"/>
       <c r="AP31" s="94" t="n"/>
       <c r="AQ31" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR31" s="93" t="n"/>
       <c r="AS31" s="93" t="n"/>
@@ -5781,7 +5781,7 @@
       <c r="AO32" s="93" t="n"/>
       <c r="AP32" s="94" t="n"/>
       <c r="AQ32" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR32" s="93" t="n"/>
       <c r="AS32" s="93" t="n"/>
@@ -5864,7 +5864,7 @@
       <c r="AO33" s="93" t="n"/>
       <c r="AP33" s="94" t="n"/>
       <c r="AQ33" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR33" s="93" t="n"/>
       <c r="AS33" s="93" t="n"/>
@@ -5946,7 +5946,7 @@
       <c r="AO34" s="93" t="n"/>
       <c r="AP34" s="94" t="n"/>
       <c r="AQ34" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR34" s="93" t="n"/>
       <c r="AS34" s="93" t="n"/>
@@ -6029,7 +6029,7 @@
       <c r="AO35" s="93" t="n"/>
       <c r="AP35" s="94" t="n"/>
       <c r="AQ35" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR35" s="93" t="n"/>
       <c r="AS35" s="93" t="n"/>
@@ -6111,7 +6111,7 @@
       <c r="AO36" s="93" t="n"/>
       <c r="AP36" s="94" t="n"/>
       <c r="AQ36" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR36" s="93" t="n"/>
       <c r="AS36" s="93" t="n"/>
@@ -6194,7 +6194,7 @@
       <c r="AO37" s="93" t="n"/>
       <c r="AP37" s="94" t="n"/>
       <c r="AQ37" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR37" s="93" t="n"/>
       <c r="AS37" s="93" t="n"/>
@@ -6277,7 +6277,7 @@
       <c r="AO38" s="93" t="n"/>
       <c r="AP38" s="94" t="n"/>
       <c r="AQ38" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR38" s="93" t="n"/>
       <c r="AS38" s="93" t="n"/>
@@ -6359,7 +6359,7 @@
       <c r="AO39" s="93" t="n"/>
       <c r="AP39" s="94" t="n"/>
       <c r="AQ39" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR39" s="93" t="n"/>
       <c r="AS39" s="93" t="n"/>
@@ -6441,7 +6441,7 @@
       <c r="AO40" s="93" t="n"/>
       <c r="AP40" s="94" t="n"/>
       <c r="AQ40" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR40" s="93" t="n"/>
       <c r="AS40" s="93" t="n"/>
@@ -6523,7 +6523,7 @@
       <c r="AO41" s="93" t="n"/>
       <c r="AP41" s="94" t="n"/>
       <c r="AQ41" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR41" s="93" t="n"/>
       <c r="AS41" s="93" t="n"/>
@@ -6606,7 +6606,7 @@
       <c r="AO42" s="93" t="n"/>
       <c r="AP42" s="94" t="n"/>
       <c r="AQ42" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR42" s="93" t="n"/>
       <c r="AS42" s="93" t="n"/>
@@ -6689,7 +6689,7 @@
       <c r="AO43" s="93" t="n"/>
       <c r="AP43" s="94" t="n"/>
       <c r="AQ43" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR43" s="93" t="n"/>
       <c r="AS43" s="93" t="n"/>
@@ -6771,7 +6771,7 @@
       <c r="AO44" s="93" t="n"/>
       <c r="AP44" s="94" t="n"/>
       <c r="AQ44" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR44" s="93" t="n"/>
       <c r="AS44" s="93" t="n"/>
@@ -6854,7 +6854,7 @@
       <c r="AO45" s="93" t="n"/>
       <c r="AP45" s="94" t="n"/>
       <c r="AQ45" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR45" s="93" t="n"/>
       <c r="AS45" s="93" t="n"/>
@@ -6937,7 +6937,7 @@
       <c r="AO46" s="93" t="n"/>
       <c r="AP46" s="94" t="n"/>
       <c r="AQ46" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR46" s="93" t="n"/>
       <c r="AS46" s="93" t="n"/>
@@ -7019,7 +7019,7 @@
       <c r="AO47" s="93" t="n"/>
       <c r="AP47" s="94" t="n"/>
       <c r="AQ47" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR47" s="93" t="n"/>
       <c r="AS47" s="93" t="n"/>
@@ -7103,7 +7103,7 @@
       <c r="AO48" s="93" t="n"/>
       <c r="AP48" s="94" t="n"/>
       <c r="AQ48" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR48" s="93" t="n"/>
       <c r="AS48" s="93" t="n"/>
@@ -7186,7 +7186,7 @@
       <c r="AO49" s="93" t="n"/>
       <c r="AP49" s="94" t="n"/>
       <c r="AQ49" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR49" s="93" t="n"/>
       <c r="AS49" s="93" t="n"/>
@@ -7269,7 +7269,7 @@
       <c r="AO50" s="93" t="n"/>
       <c r="AP50" s="94" t="n"/>
       <c r="AQ50" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR50" s="93" t="n"/>
       <c r="AS50" s="93" t="n"/>
@@ -7351,7 +7351,7 @@
       <c r="AO51" s="93" t="n"/>
       <c r="AP51" s="94" t="n"/>
       <c r="AQ51" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR51" s="93" t="n"/>
       <c r="AS51" s="93" t="n"/>
@@ -7433,7 +7433,7 @@
       <c r="AO52" s="93" t="n"/>
       <c r="AP52" s="94" t="n"/>
       <c r="AQ52" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR52" s="93" t="n"/>
       <c r="AS52" s="93" t="n"/>
@@ -7516,7 +7516,7 @@
       <c r="AO53" s="93" t="n"/>
       <c r="AP53" s="94" t="n"/>
       <c r="AQ53" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR53" s="93" t="n"/>
       <c r="AS53" s="93" t="n"/>
@@ -7599,7 +7599,7 @@
       <c r="AO54" s="93" t="n"/>
       <c r="AP54" s="94" t="n"/>
       <c r="AQ54" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR54" s="93" t="n"/>
       <c r="AS54" s="93" t="n"/>
@@ -7681,7 +7681,7 @@
       <c r="AO55" s="93" t="n"/>
       <c r="AP55" s="94" t="n"/>
       <c r="AQ55" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR55" s="93" t="n"/>
       <c r="AS55" s="93" t="n"/>
@@ -7763,7 +7763,7 @@
       <c r="AO56" s="93" t="n"/>
       <c r="AP56" s="94" t="n"/>
       <c r="AQ56" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR56" s="93" t="n"/>
       <c r="AS56" s="93" t="n"/>
@@ -7845,7 +7845,7 @@
       <c r="AO57" s="93" t="n"/>
       <c r="AP57" s="94" t="n"/>
       <c r="AQ57" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR57" s="93" t="n"/>
       <c r="AS57" s="93" t="n"/>
@@ -7927,7 +7927,7 @@
       <c r="AO58" s="93" t="n"/>
       <c r="AP58" s="94" t="n"/>
       <c r="AQ58" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR58" s="93" t="n"/>
       <c r="AS58" s="93" t="n"/>
@@ -8009,7 +8009,7 @@
       <c r="AO59" s="93" t="n"/>
       <c r="AP59" s="94" t="n"/>
       <c r="AQ59" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR59" s="93" t="n"/>
       <c r="AS59" s="93" t="n"/>
@@ -8091,7 +8091,7 @@
       <c r="AO60" s="93" t="n"/>
       <c r="AP60" s="94" t="n"/>
       <c r="AQ60" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR60" s="93" t="n"/>
       <c r="AS60" s="93" t="n"/>
@@ -8173,7 +8173,7 @@
       <c r="AO61" s="93" t="n"/>
       <c r="AP61" s="94" t="n"/>
       <c r="AQ61" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR61" s="93" t="n"/>
       <c r="AS61" s="93" t="n"/>
@@ -8255,7 +8255,7 @@
       <c r="AO62" s="93" t="n"/>
       <c r="AP62" s="94" t="n"/>
       <c r="AQ62" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR62" s="93" t="n"/>
       <c r="AS62" s="93" t="n"/>
@@ -8337,7 +8337,7 @@
       <c r="AO63" s="93" t="n"/>
       <c r="AP63" s="94" t="n"/>
       <c r="AQ63" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR63" s="93" t="n"/>
       <c r="AS63" s="93" t="n"/>
@@ -8419,7 +8419,7 @@
       <c r="AO64" s="93" t="n"/>
       <c r="AP64" s="94" t="n"/>
       <c r="AQ64" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR64" s="93" t="n"/>
       <c r="AS64" s="93" t="n"/>
@@ -8501,7 +8501,7 @@
       <c r="AO65" s="93" t="n"/>
       <c r="AP65" s="94" t="n"/>
       <c r="AQ65" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR65" s="93" t="n"/>
       <c r="AS65" s="93" t="n"/>
@@ -8582,7 +8582,7 @@
       <c r="AO66" s="93" t="n"/>
       <c r="AP66" s="94" t="n"/>
       <c r="AQ66" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR66" s="93" t="n"/>
       <c r="AS66" s="93" t="n"/>
@@ -8663,7 +8663,7 @@
       <c r="AO67" s="93" t="n"/>
       <c r="AP67" s="94" t="n"/>
       <c r="AQ67" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR67" s="93" t="n"/>
       <c r="AS67" s="93" t="n"/>
@@ -8744,7 +8744,7 @@
       <c r="AO68" s="93" t="n"/>
       <c r="AP68" s="94" t="n"/>
       <c r="AQ68" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR68" s="93" t="n"/>
       <c r="AS68" s="93" t="n"/>
@@ -8826,7 +8826,7 @@
       <c r="AO69" s="93" t="n"/>
       <c r="AP69" s="94" t="n"/>
       <c r="AQ69" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR69" s="93" t="n"/>
       <c r="AS69" s="93" t="n"/>
@@ -8908,7 +8908,7 @@
       <c r="AO70" s="93" t="n"/>
       <c r="AP70" s="94" t="n"/>
       <c r="AQ70" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR70" s="93" t="n"/>
       <c r="AS70" s="93" t="n"/>
@@ -8990,7 +8990,7 @@
       <c r="AO71" s="93" t="n"/>
       <c r="AP71" s="94" t="n"/>
       <c r="AQ71" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR71" s="93" t="n"/>
       <c r="AS71" s="93" t="n"/>
@@ -9072,7 +9072,7 @@
       <c r="AO72" s="93" t="n"/>
       <c r="AP72" s="94" t="n"/>
       <c r="AQ72" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR72" s="93" t="n"/>
       <c r="AS72" s="93" t="n"/>
@@ -9154,7 +9154,7 @@
       <c r="AO73" s="93" t="n"/>
       <c r="AP73" s="94" t="n"/>
       <c r="AQ73" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR73" s="93" t="n"/>
       <c r="AS73" s="93" t="n"/>
@@ -9236,7 +9236,7 @@
       <c r="AO74" s="93" t="n"/>
       <c r="AP74" s="94" t="n"/>
       <c r="AQ74" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR74" s="93" t="n"/>
       <c r="AS74" s="93" t="n"/>
@@ -9318,7 +9318,7 @@
       <c r="AO75" s="93" t="n"/>
       <c r="AP75" s="94" t="n"/>
       <c r="AQ75" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR75" s="93" t="n"/>
       <c r="AS75" s="93" t="n"/>
@@ -9400,7 +9400,7 @@
       <c r="AO76" s="93" t="n"/>
       <c r="AP76" s="94" t="n"/>
       <c r="AQ76" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR76" s="93" t="n"/>
       <c r="AS76" s="93" t="n"/>
@@ -9482,7 +9482,7 @@
       <c r="AO77" s="93" t="n"/>
       <c r="AP77" s="94" t="n"/>
       <c r="AQ77" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR77" s="93" t="n"/>
       <c r="AS77" s="93" t="n"/>
@@ -9563,7 +9563,7 @@
       <c r="AO78" s="93" t="n"/>
       <c r="AP78" s="94" t="n"/>
       <c r="AQ78" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR78" s="93" t="n"/>
       <c r="AS78" s="93" t="n"/>
@@ -9645,7 +9645,7 @@
       <c r="AO79" s="93" t="n"/>
       <c r="AP79" s="94" t="n"/>
       <c r="AQ79" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR79" s="93" t="n"/>
       <c r="AS79" s="93" t="n"/>
@@ -9727,7 +9727,7 @@
       <c r="AO80" s="93" t="n"/>
       <c r="AP80" s="94" t="n"/>
       <c r="AQ80" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR80" s="93" t="n"/>
       <c r="AS80" s="93" t="n"/>
@@ -9809,7 +9809,7 @@
       <c r="AO81" s="93" t="n"/>
       <c r="AP81" s="94" t="n"/>
       <c r="AQ81" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR81" s="93" t="n"/>
       <c r="AS81" s="93" t="n"/>
@@ -9891,7 +9891,7 @@
       <c r="AO82" s="93" t="n"/>
       <c r="AP82" s="94" t="n"/>
       <c r="AQ82" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR82" s="93" t="n"/>
       <c r="AS82" s="93" t="n"/>
@@ -9973,7 +9973,7 @@
       <c r="AO83" s="93" t="n"/>
       <c r="AP83" s="94" t="n"/>
       <c r="AQ83" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR83" s="93" t="n"/>
       <c r="AS83" s="93" t="n"/>
@@ -10055,7 +10055,7 @@
       <c r="AO84" s="93" t="n"/>
       <c r="AP84" s="94" t="n"/>
       <c r="AQ84" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR84" s="93" t="n"/>
       <c r="AS84" s="93" t="n"/>
@@ -10137,7 +10137,7 @@
       <c r="AO85" s="93" t="n"/>
       <c r="AP85" s="94" t="n"/>
       <c r="AQ85" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR85" s="93" t="n"/>
       <c r="AS85" s="93" t="n"/>
@@ -10219,7 +10219,7 @@
       <c r="AO86" s="93" t="n"/>
       <c r="AP86" s="94" t="n"/>
       <c r="AQ86" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR86" s="93" t="n"/>
       <c r="AS86" s="93" t="n"/>
@@ -10301,7 +10301,7 @@
       <c r="AO87" s="93" t="n"/>
       <c r="AP87" s="94" t="n"/>
       <c r="AQ87" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR87" s="93" t="n"/>
       <c r="AS87" s="93" t="n"/>
@@ -10382,7 +10382,7 @@
       <c r="AO88" s="93" t="n"/>
       <c r="AP88" s="94" t="n"/>
       <c r="AQ88" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR88" s="93" t="n"/>
       <c r="AS88" s="93" t="n"/>
@@ -10463,7 +10463,7 @@
       <c r="AO89" s="93" t="n"/>
       <c r="AP89" s="94" t="n"/>
       <c r="AQ89" s="102" t="n">
-        <v>46316</v>
+        <v>46321</v>
       </c>
       <c r="AR89" s="93" t="n"/>
       <c r="AS89" s="93" t="n"/>
@@ -10485,30 +10485,1968 @@
       <c r="BE89" s="93" t="n"/>
       <c r="BF89" s="94" t="n"/>
     </row>
-    <row r="90" ht="20.25" customHeight="1" s="92"/>
-    <row r="91" ht="20.25" customHeight="1" s="92"/>
-    <row r="92" ht="20.25" customHeight="1" s="92"/>
-    <row r="93" ht="20.25" customHeight="1" s="92"/>
-    <row r="94" ht="20.25" customHeight="1" s="92"/>
-    <row r="95" ht="20.25" customHeight="1" s="92"/>
-    <row r="96" ht="20.25" customHeight="1" s="92"/>
-    <row r="97" ht="20.25" customHeight="1" s="92"/>
-    <row r="98" ht="20.25" customHeight="1" s="92"/>
-    <row r="99" ht="20.25" customHeight="1" s="92"/>
-    <row r="100" ht="20.25" customHeight="1" s="92"/>
-    <row r="101" ht="20.25" customHeight="1" s="92"/>
-    <row r="102" ht="20.25" customHeight="1" s="92"/>
-    <row r="103" ht="20.25" customHeight="1" s="92"/>
-    <row r="104" ht="20.25" customHeight="1" s="92"/>
-    <row r="105" ht="20.25" customHeight="1" s="92"/>
-    <row r="106" ht="20.25" customHeight="1" s="92"/>
-    <row r="107" ht="20.25" customHeight="1" s="92"/>
-    <row r="108" ht="20.25" customHeight="1" s="92"/>
-    <row r="109" ht="20.25" customHeight="1" s="92"/>
-    <row r="110" ht="20.25" customHeight="1" s="92"/>
-    <row r="111" ht="20.25" customHeight="1" s="92"/>
-    <row r="112" ht="20.25" customHeight="1" s="92"/>
-    <row r="113" ht="20.25" customHeight="1" s="92"/>
+    <row r="90" ht="75" customHeight="1" s="92">
+      <c r="B90" s="42" t="n">
+        <v>86</v>
+      </c>
+      <c r="C90" s="93" t="n"/>
+      <c r="D90" s="94" t="n"/>
+      <c r="E90" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：记录中心菜单项与图标
+前置条件：控制台已打开
+操作步骤：1. 观察左侧菜单
+2. 点击「03 记录中心」</t>
+        </is>
+      </c>
+      <c r="F90" s="93" t="n"/>
+      <c r="G90" s="93" t="n"/>
+      <c r="H90" s="93" t="n"/>
+      <c r="I90" s="93" t="n"/>
+      <c r="J90" s="93" t="n"/>
+      <c r="K90" s="93" t="n"/>
+      <c r="L90" s="93" t="n"/>
+      <c r="M90" s="93" t="n"/>
+      <c r="N90" s="93" t="n"/>
+      <c r="O90" s="93" t="n"/>
+      <c r="P90" s="93" t="n"/>
+      <c r="Q90" s="93" t="n"/>
+      <c r="R90" s="93" t="n"/>
+      <c r="S90" s="93" t="n"/>
+      <c r="T90" s="93" t="n"/>
+      <c r="U90" s="94" t="n"/>
+      <c r="V90" s="52" t="inlineStr">
+        <is>
+          <t>菜单第二项之下显示「03 记录中心」并带数据库图标；点击后右侧内容切换到记录页，页面不整体刷新</t>
+        </is>
+      </c>
+      <c r="W90" s="93" t="n"/>
+      <c r="X90" s="93" t="n"/>
+      <c r="Y90" s="93" t="n"/>
+      <c r="Z90" s="93" t="n"/>
+      <c r="AA90" s="93" t="n"/>
+      <c r="AB90" s="93" t="n"/>
+      <c r="AC90" s="93" t="n"/>
+      <c r="AD90" s="93" t="n"/>
+      <c r="AE90" s="93" t="n"/>
+      <c r="AF90" s="93" t="n"/>
+      <c r="AG90" s="93" t="n"/>
+      <c r="AH90" s="93" t="n"/>
+      <c r="AI90" s="93" t="n"/>
+      <c r="AJ90" s="93" t="n"/>
+      <c r="AK90" s="93" t="n"/>
+      <c r="AL90" s="94" t="n"/>
+      <c r="AM90" s="101" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="AN90" s="93" t="n"/>
+      <c r="AO90" s="93" t="n"/>
+      <c r="AP90" s="94" t="n"/>
+      <c r="AQ90" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR90" s="93" t="n"/>
+      <c r="AS90" s="93" t="n"/>
+      <c r="AT90" s="94" t="n"/>
+      <c r="AU90" s="101" t="n"/>
+      <c r="AV90" s="93" t="n"/>
+      <c r="AW90" s="93" t="n"/>
+      <c r="AX90" s="94" t="n"/>
+      <c r="AY90" s="42" t="n"/>
+      <c r="AZ90" s="93" t="n"/>
+      <c r="BA90" s="93" t="n"/>
+      <c r="BB90" s="94" t="n"/>
+      <c r="BC90" s="101" t="inlineStr">
+        <is>
+          <t>见记录中心图1</t>
+        </is>
+      </c>
+      <c r="BD90" s="93" t="n"/>
+      <c r="BE90" s="93" t="n"/>
+      <c r="BF90" s="94" t="n"/>
+    </row>
+    <row r="91" ht="75" customHeight="1" s="92">
+      <c r="B91" s="42" t="n">
+        <v>87</v>
+      </c>
+      <c r="C91" s="93" t="n"/>
+      <c r="D91" s="94" t="n"/>
+      <c r="E91" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：数据库状态徽标
+前置条件：后端已启动
+操作步骤：1. 观察记录中心卡片标题右侧徽标
+2. 停止数据库后刷新</t>
+        </is>
+      </c>
+      <c r="F91" s="93" t="n"/>
+      <c r="G91" s="93" t="n"/>
+      <c r="H91" s="93" t="n"/>
+      <c r="I91" s="93" t="n"/>
+      <c r="J91" s="93" t="n"/>
+      <c r="K91" s="93" t="n"/>
+      <c r="L91" s="93" t="n"/>
+      <c r="M91" s="93" t="n"/>
+      <c r="N91" s="93" t="n"/>
+      <c r="O91" s="93" t="n"/>
+      <c r="P91" s="93" t="n"/>
+      <c r="Q91" s="93" t="n"/>
+      <c r="R91" s="93" t="n"/>
+      <c r="S91" s="93" t="n"/>
+      <c r="T91" s="93" t="n"/>
+      <c r="U91" s="94" t="n"/>
+      <c r="V91" s="52" t="inlineStr">
+        <is>
+          <t>连接正常时显示 MySQL 版本号（如 8.0.44）；数据库不可用时显示「数据库未连接」并提示原因，页面不崩</t>
+        </is>
+      </c>
+      <c r="W91" s="93" t="n"/>
+      <c r="X91" s="93" t="n"/>
+      <c r="Y91" s="93" t="n"/>
+      <c r="Z91" s="93" t="n"/>
+      <c r="AA91" s="93" t="n"/>
+      <c r="AB91" s="93" t="n"/>
+      <c r="AC91" s="93" t="n"/>
+      <c r="AD91" s="93" t="n"/>
+      <c r="AE91" s="93" t="n"/>
+      <c r="AF91" s="93" t="n"/>
+      <c r="AG91" s="93" t="n"/>
+      <c r="AH91" s="93" t="n"/>
+      <c r="AI91" s="93" t="n"/>
+      <c r="AJ91" s="93" t="n"/>
+      <c r="AK91" s="93" t="n"/>
+      <c r="AL91" s="94" t="n"/>
+      <c r="AM91" s="101" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AN91" s="93" t="n"/>
+      <c r="AO91" s="93" t="n"/>
+      <c r="AP91" s="94" t="n"/>
+      <c r="AQ91" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR91" s="93" t="n"/>
+      <c r="AS91" s="93" t="n"/>
+      <c r="AT91" s="94" t="n"/>
+      <c r="AU91" s="101" t="n"/>
+      <c r="AV91" s="93" t="n"/>
+      <c r="AW91" s="93" t="n"/>
+      <c r="AX91" s="94" t="n"/>
+      <c r="AY91" s="42" t="n"/>
+      <c r="AZ91" s="93" t="n"/>
+      <c r="BA91" s="93" t="n"/>
+      <c r="BB91" s="94" t="n"/>
+      <c r="BC91" s="101" t="inlineStr">
+        <is>
+          <t>见记录中心图1</t>
+        </is>
+      </c>
+      <c r="BD91" s="93" t="n"/>
+      <c r="BE91" s="93" t="n"/>
+      <c r="BF91" s="94" t="n"/>
+    </row>
+    <row r="92" ht="75" customHeight="1" s="92">
+      <c r="B92" s="42" t="n">
+        <v>88</v>
+      </c>
+      <c r="C92" s="93" t="n"/>
+      <c r="D92" s="94" t="n"/>
+      <c r="E92" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：分拣记录列表结构
+前置条件：已有分拣记录
+操作步骤：1. 观察表格列与内容</t>
+        </is>
+      </c>
+      <c r="F92" s="93" t="n"/>
+      <c r="G92" s="93" t="n"/>
+      <c r="H92" s="93" t="n"/>
+      <c r="I92" s="93" t="n"/>
+      <c r="J92" s="93" t="n"/>
+      <c r="K92" s="93" t="n"/>
+      <c r="L92" s="93" t="n"/>
+      <c r="M92" s="93" t="n"/>
+      <c r="N92" s="93" t="n"/>
+      <c r="O92" s="93" t="n"/>
+      <c r="P92" s="93" t="n"/>
+      <c r="Q92" s="93" t="n"/>
+      <c r="R92" s="93" t="n"/>
+      <c r="S92" s="93" t="n"/>
+      <c r="T92" s="93" t="n"/>
+      <c r="U92" s="94" t="n"/>
+      <c r="V92" s="52" t="inlineStr">
+        <is>
+          <t>列完整：缩略图 / 时间 / 识别结果 / 置信度 / 桶位 / 来源 / 串口 / 人工判定 / 训练集 / 操作；缩略图为 320px 画面</t>
+        </is>
+      </c>
+      <c r="W92" s="93" t="n"/>
+      <c r="X92" s="93" t="n"/>
+      <c r="Y92" s="93" t="n"/>
+      <c r="Z92" s="93" t="n"/>
+      <c r="AA92" s="93" t="n"/>
+      <c r="AB92" s="93" t="n"/>
+      <c r="AC92" s="93" t="n"/>
+      <c r="AD92" s="93" t="n"/>
+      <c r="AE92" s="93" t="n"/>
+      <c r="AF92" s="93" t="n"/>
+      <c r="AG92" s="93" t="n"/>
+      <c r="AH92" s="93" t="n"/>
+      <c r="AI92" s="93" t="n"/>
+      <c r="AJ92" s="93" t="n"/>
+      <c r="AK92" s="93" t="n"/>
+      <c r="AL92" s="94" t="n"/>
+      <c r="AM92" s="101" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AN92" s="93" t="n"/>
+      <c r="AO92" s="93" t="n"/>
+      <c r="AP92" s="94" t="n"/>
+      <c r="AQ92" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR92" s="93" t="n"/>
+      <c r="AS92" s="93" t="n"/>
+      <c r="AT92" s="94" t="n"/>
+      <c r="AU92" s="101" t="n"/>
+      <c r="AV92" s="93" t="n"/>
+      <c r="AW92" s="93" t="n"/>
+      <c r="AX92" s="94" t="n"/>
+      <c r="AY92" s="42" t="n"/>
+      <c r="AZ92" s="93" t="n"/>
+      <c r="BA92" s="93" t="n"/>
+      <c r="BB92" s="94" t="n"/>
+      <c r="BC92" s="101" t="inlineStr">
+        <is>
+          <t>见记录中心图1</t>
+        </is>
+      </c>
+      <c r="BD92" s="93" t="n"/>
+      <c r="BE92" s="93" t="n"/>
+      <c r="BF92" s="94" t="n"/>
+    </row>
+    <row r="93" ht="75" customHeight="1" s="92">
+      <c r="B93" s="42" t="n">
+        <v>89</v>
+      </c>
+      <c r="C93" s="93" t="n"/>
+      <c r="D93" s="94" t="n"/>
+      <c r="E93" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：记录筛选组合
+前置条件：已有多种记录
+操作步骤：1. 依次用「未判定/正确/已纠正」+ 类别 + 来源 + 训练集 + 日期范围 + 关键字筛选</t>
+        </is>
+      </c>
+      <c r="F93" s="93" t="n"/>
+      <c r="G93" s="93" t="n"/>
+      <c r="H93" s="93" t="n"/>
+      <c r="I93" s="93" t="n"/>
+      <c r="J93" s="93" t="n"/>
+      <c r="K93" s="93" t="n"/>
+      <c r="L93" s="93" t="n"/>
+      <c r="M93" s="93" t="n"/>
+      <c r="N93" s="93" t="n"/>
+      <c r="O93" s="93" t="n"/>
+      <c r="P93" s="93" t="n"/>
+      <c r="Q93" s="93" t="n"/>
+      <c r="R93" s="93" t="n"/>
+      <c r="S93" s="93" t="n"/>
+      <c r="T93" s="93" t="n"/>
+      <c r="U93" s="94" t="n"/>
+      <c r="V93" s="52" t="inlineStr">
+        <is>
+          <t>筛选条件可叠加，结果即时变化；清空后恢复全部；筛选后分页总数同步更新</t>
+        </is>
+      </c>
+      <c r="W93" s="93" t="n"/>
+      <c r="X93" s="93" t="n"/>
+      <c r="Y93" s="93" t="n"/>
+      <c r="Z93" s="93" t="n"/>
+      <c r="AA93" s="93" t="n"/>
+      <c r="AB93" s="93" t="n"/>
+      <c r="AC93" s="93" t="n"/>
+      <c r="AD93" s="93" t="n"/>
+      <c r="AE93" s="93" t="n"/>
+      <c r="AF93" s="93" t="n"/>
+      <c r="AG93" s="93" t="n"/>
+      <c r="AH93" s="93" t="n"/>
+      <c r="AI93" s="93" t="n"/>
+      <c r="AJ93" s="93" t="n"/>
+      <c r="AK93" s="93" t="n"/>
+      <c r="AL93" s="94" t="n"/>
+      <c r="AM93" s="101" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="AN93" s="93" t="n"/>
+      <c r="AO93" s="93" t="n"/>
+      <c r="AP93" s="94" t="n"/>
+      <c r="AQ93" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR93" s="93" t="n"/>
+      <c r="AS93" s="93" t="n"/>
+      <c r="AT93" s="94" t="n"/>
+      <c r="AU93" s="101" t="n"/>
+      <c r="AV93" s="93" t="n"/>
+      <c r="AW93" s="93" t="n"/>
+      <c r="AX93" s="94" t="n"/>
+      <c r="AY93" s="42" t="n"/>
+      <c r="AZ93" s="93" t="n"/>
+      <c r="BA93" s="93" t="n"/>
+      <c r="BB93" s="94" t="n"/>
+      <c r="BC93" s="101" t="inlineStr">
+        <is>
+          <t>见记录中心图2</t>
+        </is>
+      </c>
+      <c r="BD93" s="93" t="n"/>
+      <c r="BE93" s="93" t="n"/>
+      <c r="BF93" s="94" t="n"/>
+    </row>
+    <row r="94" ht="75" customHeight="1" s="92">
+      <c r="B94" s="42" t="n">
+        <v>90</v>
+      </c>
+      <c r="C94" s="93" t="n"/>
+      <c r="D94" s="94" t="n"/>
+      <c r="E94" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：记录详情抽屉
+前置条件：已有带图片的记录
+操作步骤：1. 点击某行「查看」</t>
+        </is>
+      </c>
+      <c r="F94" s="93" t="n"/>
+      <c r="G94" s="93" t="n"/>
+      <c r="H94" s="93" t="n"/>
+      <c r="I94" s="93" t="n"/>
+      <c r="J94" s="93" t="n"/>
+      <c r="K94" s="93" t="n"/>
+      <c r="L94" s="93" t="n"/>
+      <c r="M94" s="93" t="n"/>
+      <c r="N94" s="93" t="n"/>
+      <c r="O94" s="93" t="n"/>
+      <c r="P94" s="93" t="n"/>
+      <c r="Q94" s="93" t="n"/>
+      <c r="R94" s="93" t="n"/>
+      <c r="S94" s="93" t="n"/>
+      <c r="T94" s="93" t="n"/>
+      <c r="U94" s="94" t="n"/>
+      <c r="V94" s="52" t="inlineStr">
+        <is>
+          <t>抽屉展示带框大图、原始无框帧与 12 项字段（时间/类别/置信度/bbox/来源/桶位/角度/串口/判定/训练集/模型/会话）</t>
+        </is>
+      </c>
+      <c r="W94" s="93" t="n"/>
+      <c r="X94" s="93" t="n"/>
+      <c r="Y94" s="93" t="n"/>
+      <c r="Z94" s="93" t="n"/>
+      <c r="AA94" s="93" t="n"/>
+      <c r="AB94" s="93" t="n"/>
+      <c r="AC94" s="93" t="n"/>
+      <c r="AD94" s="93" t="n"/>
+      <c r="AE94" s="93" t="n"/>
+      <c r="AF94" s="93" t="n"/>
+      <c r="AG94" s="93" t="n"/>
+      <c r="AH94" s="93" t="n"/>
+      <c r="AI94" s="93" t="n"/>
+      <c r="AJ94" s="93" t="n"/>
+      <c r="AK94" s="93" t="n"/>
+      <c r="AL94" s="94" t="n"/>
+      <c r="AM94" s="101" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="AN94" s="93" t="n"/>
+      <c r="AO94" s="93" t="n"/>
+      <c r="AP94" s="94" t="n"/>
+      <c r="AQ94" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR94" s="93" t="n"/>
+      <c r="AS94" s="93" t="n"/>
+      <c r="AT94" s="94" t="n"/>
+      <c r="AU94" s="101" t="n"/>
+      <c r="AV94" s="93" t="n"/>
+      <c r="AW94" s="93" t="n"/>
+      <c r="AX94" s="94" t="n"/>
+      <c r="AY94" s="42" t="n"/>
+      <c r="AZ94" s="93" t="n"/>
+      <c r="BA94" s="93" t="n"/>
+      <c r="BB94" s="94" t="n"/>
+      <c r="BC94" s="101" t="inlineStr">
+        <is>
+          <t>见记录中心图3</t>
+        </is>
+      </c>
+      <c r="BD94" s="93" t="n"/>
+      <c r="BE94" s="93" t="n"/>
+      <c r="BF94" s="94" t="n"/>
+    </row>
+    <row r="95" ht="75" customHeight="1" s="92">
+      <c r="B95" s="42" t="n">
+        <v>91</v>
+      </c>
+      <c r="C95" s="93" t="n"/>
+      <c r="D95" s="94" t="n"/>
+      <c r="E95" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：人工判定：识别正确
+前置条件：已有未判定记录
+操作步骤：1. 点击该行「正确」
+2. 刷新页面查看</t>
+        </is>
+      </c>
+      <c r="F95" s="93" t="n"/>
+      <c r="G95" s="93" t="n"/>
+      <c r="H95" s="93" t="n"/>
+      <c r="I95" s="93" t="n"/>
+      <c r="J95" s="93" t="n"/>
+      <c r="K95" s="93" t="n"/>
+      <c r="L95" s="93" t="n"/>
+      <c r="M95" s="93" t="n"/>
+      <c r="N95" s="93" t="n"/>
+      <c r="O95" s="93" t="n"/>
+      <c r="P95" s="93" t="n"/>
+      <c r="Q95" s="93" t="n"/>
+      <c r="R95" s="93" t="n"/>
+      <c r="S95" s="93" t="n"/>
+      <c r="T95" s="93" t="n"/>
+      <c r="U95" s="94" t="n"/>
+      <c r="V95" s="52" t="inlineStr">
+        <is>
+          <t>判定状态变为「正确」并持久化；统计行的「已判定正确」计数 +1</t>
+        </is>
+      </c>
+      <c r="W95" s="93" t="n"/>
+      <c r="X95" s="93" t="n"/>
+      <c r="Y95" s="93" t="n"/>
+      <c r="Z95" s="93" t="n"/>
+      <c r="AA95" s="93" t="n"/>
+      <c r="AB95" s="93" t="n"/>
+      <c r="AC95" s="93" t="n"/>
+      <c r="AD95" s="93" t="n"/>
+      <c r="AE95" s="93" t="n"/>
+      <c r="AF95" s="93" t="n"/>
+      <c r="AG95" s="93" t="n"/>
+      <c r="AH95" s="93" t="n"/>
+      <c r="AI95" s="93" t="n"/>
+      <c r="AJ95" s="93" t="n"/>
+      <c r="AK95" s="93" t="n"/>
+      <c r="AL95" s="94" t="n"/>
+      <c r="AM95" s="101" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AN95" s="93" t="n"/>
+      <c r="AO95" s="93" t="n"/>
+      <c r="AP95" s="94" t="n"/>
+      <c r="AQ95" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR95" s="93" t="n"/>
+      <c r="AS95" s="93" t="n"/>
+      <c r="AT95" s="94" t="n"/>
+      <c r="AU95" s="101" t="n"/>
+      <c r="AV95" s="93" t="n"/>
+      <c r="AW95" s="93" t="n"/>
+      <c r="AX95" s="94" t="n"/>
+      <c r="AY95" s="42" t="n"/>
+      <c r="AZ95" s="93" t="n"/>
+      <c r="BA95" s="93" t="n"/>
+      <c r="BB95" s="94" t="n"/>
+      <c r="BC95" s="101" t="inlineStr">
+        <is>
+          <t>见记录中心图2</t>
+        </is>
+      </c>
+      <c r="BD95" s="93" t="n"/>
+      <c r="BE95" s="93" t="n"/>
+      <c r="BF95" s="94" t="n"/>
+    </row>
+    <row r="96" ht="75" customHeight="1" s="92">
+      <c r="B96" s="42" t="n">
+        <v>92</v>
+      </c>
+      <c r="C96" s="93" t="n"/>
+      <c r="D96" s="94" t="n"/>
+      <c r="E96" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：人工判定：识别错误并选真实类别
+前置条件：已有未判定记录
+操作步骤：1. 点击「错误」
+2. 在弹窗选择真实类别后保存</t>
+        </is>
+      </c>
+      <c r="F96" s="93" t="n"/>
+      <c r="G96" s="93" t="n"/>
+      <c r="H96" s="93" t="n"/>
+      <c r="I96" s="93" t="n"/>
+      <c r="J96" s="93" t="n"/>
+      <c r="K96" s="93" t="n"/>
+      <c r="L96" s="93" t="n"/>
+      <c r="M96" s="93" t="n"/>
+      <c r="N96" s="93" t="n"/>
+      <c r="O96" s="93" t="n"/>
+      <c r="P96" s="93" t="n"/>
+      <c r="Q96" s="93" t="n"/>
+      <c r="R96" s="93" t="n"/>
+      <c r="S96" s="93" t="n"/>
+      <c r="T96" s="93" t="n"/>
+      <c r="U96" s="94" t="n"/>
+      <c r="V96" s="52" t="inlineStr">
+        <is>
+          <t>弹窗强制选择真实类别（不选则提示）；保存后显示「已纠正 → 真实类别」，预测类别保留用于对比</t>
+        </is>
+      </c>
+      <c r="W96" s="93" t="n"/>
+      <c r="X96" s="93" t="n"/>
+      <c r="Y96" s="93" t="n"/>
+      <c r="Z96" s="93" t="n"/>
+      <c r="AA96" s="93" t="n"/>
+      <c r="AB96" s="93" t="n"/>
+      <c r="AC96" s="93" t="n"/>
+      <c r="AD96" s="93" t="n"/>
+      <c r="AE96" s="93" t="n"/>
+      <c r="AF96" s="93" t="n"/>
+      <c r="AG96" s="93" t="n"/>
+      <c r="AH96" s="93" t="n"/>
+      <c r="AI96" s="93" t="n"/>
+      <c r="AJ96" s="93" t="n"/>
+      <c r="AK96" s="93" t="n"/>
+      <c r="AL96" s="94" t="n"/>
+      <c r="AM96" s="101" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AN96" s="93" t="n"/>
+      <c r="AO96" s="93" t="n"/>
+      <c r="AP96" s="94" t="n"/>
+      <c r="AQ96" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR96" s="93" t="n"/>
+      <c r="AS96" s="93" t="n"/>
+      <c r="AT96" s="94" t="n"/>
+      <c r="AU96" s="101" t="n"/>
+      <c r="AV96" s="93" t="n"/>
+      <c r="AW96" s="93" t="n"/>
+      <c r="AX96" s="94" t="n"/>
+      <c r="AY96" s="42" t="n"/>
+      <c r="AZ96" s="93" t="n"/>
+      <c r="BA96" s="93" t="n"/>
+      <c r="BB96" s="94" t="n"/>
+      <c r="BC96" s="101" t="inlineStr">
+        <is>
+          <t>见记录中心图2</t>
+        </is>
+      </c>
+      <c r="BD96" s="93" t="n"/>
+      <c r="BE96" s="93" t="n"/>
+      <c r="BF96" s="94" t="n"/>
+    </row>
+    <row r="97" ht="75" customHeight="1" s="92">
+      <c r="B97" s="42" t="n">
+        <v>93</v>
+      </c>
+      <c r="C97" s="93" t="n"/>
+      <c r="D97" s="94" t="n"/>
+      <c r="E97" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：加入训练集按钮
+前置条件：记录已有原始帧
+操作步骤：1. 点击「入训练集」
+2. 检查训练集索引与磁盘</t>
+        </is>
+      </c>
+      <c r="F97" s="93" t="n"/>
+      <c r="G97" s="93" t="n"/>
+      <c r="H97" s="93" t="n"/>
+      <c r="I97" s="93" t="n"/>
+      <c r="J97" s="93" t="n"/>
+      <c r="K97" s="93" t="n"/>
+      <c r="L97" s="93" t="n"/>
+      <c r="M97" s="93" t="n"/>
+      <c r="N97" s="93" t="n"/>
+      <c r="O97" s="93" t="n"/>
+      <c r="P97" s="93" t="n"/>
+      <c r="Q97" s="93" t="n"/>
+      <c r="R97" s="93" t="n"/>
+      <c r="S97" s="93" t="n"/>
+      <c r="T97" s="93" t="n"/>
+      <c r="U97" s="94" t="n"/>
+      <c r="V97" s="52" t="inlineStr">
+        <is>
+          <t>按钮置灰并显示「已加入」；图片按类别落到 training/captures/&lt;类别&gt;/；索引出现该图并可通过 record_id 反查</t>
+        </is>
+      </c>
+      <c r="W97" s="93" t="n"/>
+      <c r="X97" s="93" t="n"/>
+      <c r="Y97" s="93" t="n"/>
+      <c r="Z97" s="93" t="n"/>
+      <c r="AA97" s="93" t="n"/>
+      <c r="AB97" s="93" t="n"/>
+      <c r="AC97" s="93" t="n"/>
+      <c r="AD97" s="93" t="n"/>
+      <c r="AE97" s="93" t="n"/>
+      <c r="AF97" s="93" t="n"/>
+      <c r="AG97" s="93" t="n"/>
+      <c r="AH97" s="93" t="n"/>
+      <c r="AI97" s="93" t="n"/>
+      <c r="AJ97" s="93" t="n"/>
+      <c r="AK97" s="93" t="n"/>
+      <c r="AL97" s="94" t="n"/>
+      <c r="AM97" s="101" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AN97" s="93" t="n"/>
+      <c r="AO97" s="93" t="n"/>
+      <c r="AP97" s="94" t="n"/>
+      <c r="AQ97" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR97" s="93" t="n"/>
+      <c r="AS97" s="93" t="n"/>
+      <c r="AT97" s="94" t="n"/>
+      <c r="AU97" s="101" t="n"/>
+      <c r="AV97" s="93" t="n"/>
+      <c r="AW97" s="93" t="n"/>
+      <c r="AX97" s="94" t="n"/>
+      <c r="AY97" s="42" t="n"/>
+      <c r="AZ97" s="93" t="n"/>
+      <c r="BA97" s="93" t="n"/>
+      <c r="BB97" s="94" t="n"/>
+      <c r="BC97" s="101" t="inlineStr">
+        <is>
+          <t>见记录中心图2</t>
+        </is>
+      </c>
+      <c r="BD97" s="93" t="n"/>
+      <c r="BE97" s="93" t="n"/>
+      <c r="BF97" s="94" t="n"/>
+    </row>
+    <row r="98" ht="75" customHeight="1" s="92">
+      <c r="B98" s="42" t="n">
+        <v>94</v>
+      </c>
+      <c r="C98" s="93" t="n"/>
+      <c r="D98" s="94" t="n"/>
+      <c r="E98" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：删除分拣记录
+前置条件：已有记录
+操作步骤：1. 点击某行「删除」
+2. 刷新列表与数据库</t>
+        </is>
+      </c>
+      <c r="F98" s="93" t="n"/>
+      <c r="G98" s="93" t="n"/>
+      <c r="H98" s="93" t="n"/>
+      <c r="I98" s="93" t="n"/>
+      <c r="J98" s="93" t="n"/>
+      <c r="K98" s="93" t="n"/>
+      <c r="L98" s="93" t="n"/>
+      <c r="M98" s="93" t="n"/>
+      <c r="N98" s="93" t="n"/>
+      <c r="O98" s="93" t="n"/>
+      <c r="P98" s="93" t="n"/>
+      <c r="Q98" s="93" t="n"/>
+      <c r="R98" s="93" t="n"/>
+      <c r="S98" s="93" t="n"/>
+      <c r="T98" s="93" t="n"/>
+      <c r="U98" s="94" t="n"/>
+      <c r="V98" s="52" t="inlineStr">
+        <is>
+          <t>该记录从列表与数据库消失，图片数据一同删除；分页与统计同步更新</t>
+        </is>
+      </c>
+      <c r="W98" s="93" t="n"/>
+      <c r="X98" s="93" t="n"/>
+      <c r="Y98" s="93" t="n"/>
+      <c r="Z98" s="93" t="n"/>
+      <c r="AA98" s="93" t="n"/>
+      <c r="AB98" s="93" t="n"/>
+      <c r="AC98" s="93" t="n"/>
+      <c r="AD98" s="93" t="n"/>
+      <c r="AE98" s="93" t="n"/>
+      <c r="AF98" s="93" t="n"/>
+      <c r="AG98" s="93" t="n"/>
+      <c r="AH98" s="93" t="n"/>
+      <c r="AI98" s="93" t="n"/>
+      <c r="AJ98" s="93" t="n"/>
+      <c r="AK98" s="93" t="n"/>
+      <c r="AL98" s="94" t="n"/>
+      <c r="AM98" s="101" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="AN98" s="93" t="n"/>
+      <c r="AO98" s="93" t="n"/>
+      <c r="AP98" s="94" t="n"/>
+      <c r="AQ98" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR98" s="93" t="n"/>
+      <c r="AS98" s="93" t="n"/>
+      <c r="AT98" s="94" t="n"/>
+      <c r="AU98" s="101" t="n"/>
+      <c r="AV98" s="93" t="n"/>
+      <c r="AW98" s="93" t="n"/>
+      <c r="AX98" s="94" t="n"/>
+      <c r="AY98" s="42" t="n"/>
+      <c r="AZ98" s="93" t="n"/>
+      <c r="BA98" s="93" t="n"/>
+      <c r="BB98" s="94" t="n"/>
+      <c r="BC98" s="101" t="inlineStr">
+        <is>
+          <t>见记录中心图2</t>
+        </is>
+      </c>
+      <c r="BD98" s="93" t="n"/>
+      <c r="BE98" s="93" t="n"/>
+      <c r="BF98" s="94" t="n"/>
+    </row>
+    <row r="99" ht="75" customHeight="1" s="92">
+      <c r="B99" s="42" t="n">
+        <v>95</v>
+      </c>
+      <c r="C99" s="93" t="n"/>
+      <c r="D99" s="94" t="n"/>
+      <c r="E99" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：统计卡片（类别 / 桶位 / 天）
+前置条件：已有分拣记录
+操作步骤：1. 观察「统计 · 训练集索引」左侧与右上</t>
+        </is>
+      </c>
+      <c r="F99" s="93" t="n"/>
+      <c r="G99" s="93" t="n"/>
+      <c r="H99" s="93" t="n"/>
+      <c r="I99" s="93" t="n"/>
+      <c r="J99" s="93" t="n"/>
+      <c r="K99" s="93" t="n"/>
+      <c r="L99" s="93" t="n"/>
+      <c r="M99" s="93" t="n"/>
+      <c r="N99" s="93" t="n"/>
+      <c r="O99" s="93" t="n"/>
+      <c r="P99" s="93" t="n"/>
+      <c r="Q99" s="93" t="n"/>
+      <c r="R99" s="93" t="n"/>
+      <c r="S99" s="93" t="n"/>
+      <c r="T99" s="93" t="n"/>
+      <c r="U99" s="94" t="n"/>
+      <c r="V99" s="52" t="inlineStr">
+        <is>
+          <t>按类别、按物理桶、按天三组条形图数值与记录一致；比例条长度与数值成比例</t>
+        </is>
+      </c>
+      <c r="W99" s="93" t="n"/>
+      <c r="X99" s="93" t="n"/>
+      <c r="Y99" s="93" t="n"/>
+      <c r="Z99" s="93" t="n"/>
+      <c r="AA99" s="93" t="n"/>
+      <c r="AB99" s="93" t="n"/>
+      <c r="AC99" s="93" t="n"/>
+      <c r="AD99" s="93" t="n"/>
+      <c r="AE99" s="93" t="n"/>
+      <c r="AF99" s="93" t="n"/>
+      <c r="AG99" s="93" t="n"/>
+      <c r="AH99" s="93" t="n"/>
+      <c r="AI99" s="93" t="n"/>
+      <c r="AJ99" s="93" t="n"/>
+      <c r="AK99" s="93" t="n"/>
+      <c r="AL99" s="94" t="n"/>
+      <c r="AM99" s="101" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="AN99" s="93" t="n"/>
+      <c r="AO99" s="93" t="n"/>
+      <c r="AP99" s="94" t="n"/>
+      <c r="AQ99" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR99" s="93" t="n"/>
+      <c r="AS99" s="93" t="n"/>
+      <c r="AT99" s="94" t="n"/>
+      <c r="AU99" s="101" t="n"/>
+      <c r="AV99" s="93" t="n"/>
+      <c r="AW99" s="93" t="n"/>
+      <c r="AX99" s="94" t="n"/>
+      <c r="AY99" s="42" t="n"/>
+      <c r="AZ99" s="93" t="n"/>
+      <c r="BA99" s="93" t="n"/>
+      <c r="BB99" s="94" t="n"/>
+      <c r="BC99" s="101" t="inlineStr">
+        <is>
+          <t>见记录中心图4</t>
+        </is>
+      </c>
+      <c r="BD99" s="93" t="n"/>
+      <c r="BE99" s="93" t="n"/>
+      <c r="BF99" s="94" t="n"/>
+    </row>
+    <row r="100" ht="75" customHeight="1" s="92">
+      <c r="B100" s="42" t="n">
+        <v>96</v>
+      </c>
+      <c r="C100" s="93" t="n"/>
+      <c r="D100" s="94" t="n"/>
+      <c r="E100" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：训练集索引浏览
+前置条件：已回填历史抓拍
+操作步骤：1. 观察训练集索引列表
+2. 翻页</t>
+        </is>
+      </c>
+      <c r="F100" s="93" t="n"/>
+      <c r="G100" s="93" t="n"/>
+      <c r="H100" s="93" t="n"/>
+      <c r="I100" s="93" t="n"/>
+      <c r="J100" s="93" t="n"/>
+      <c r="K100" s="93" t="n"/>
+      <c r="L100" s="93" t="n"/>
+      <c r="M100" s="93" t="n"/>
+      <c r="N100" s="93" t="n"/>
+      <c r="O100" s="93" t="n"/>
+      <c r="P100" s="93" t="n"/>
+      <c r="Q100" s="93" t="n"/>
+      <c r="R100" s="93" t="n"/>
+      <c r="S100" s="93" t="n"/>
+      <c r="T100" s="93" t="n"/>
+      <c r="U100" s="94" t="n"/>
+      <c r="V100" s="52" t="inlineStr">
+        <is>
+          <t>显示缩略图 / 路径 / 类别 / 划分 / 标注 / 来源；分页总数与实际图片数一致（实测 1635 张）</t>
+        </is>
+      </c>
+      <c r="W100" s="93" t="n"/>
+      <c r="X100" s="93" t="n"/>
+      <c r="Y100" s="93" t="n"/>
+      <c r="Z100" s="93" t="n"/>
+      <c r="AA100" s="93" t="n"/>
+      <c r="AB100" s="93" t="n"/>
+      <c r="AC100" s="93" t="n"/>
+      <c r="AD100" s="93" t="n"/>
+      <c r="AE100" s="93" t="n"/>
+      <c r="AF100" s="93" t="n"/>
+      <c r="AG100" s="93" t="n"/>
+      <c r="AH100" s="93" t="n"/>
+      <c r="AI100" s="93" t="n"/>
+      <c r="AJ100" s="93" t="n"/>
+      <c r="AK100" s="93" t="n"/>
+      <c r="AL100" s="94" t="n"/>
+      <c r="AM100" s="101" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AN100" s="93" t="n"/>
+      <c r="AO100" s="93" t="n"/>
+      <c r="AP100" s="94" t="n"/>
+      <c r="AQ100" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR100" s="93" t="n"/>
+      <c r="AS100" s="93" t="n"/>
+      <c r="AT100" s="94" t="n"/>
+      <c r="AU100" s="101" t="n"/>
+      <c r="AV100" s="93" t="n"/>
+      <c r="AW100" s="93" t="n"/>
+      <c r="AX100" s="94" t="n"/>
+      <c r="AY100" s="42" t="n"/>
+      <c r="AZ100" s="93" t="n"/>
+      <c r="BA100" s="93" t="n"/>
+      <c r="BB100" s="94" t="n"/>
+      <c r="BC100" s="101" t="inlineStr">
+        <is>
+          <t>见记录中心图4</t>
+        </is>
+      </c>
+      <c r="BD100" s="93" t="n"/>
+      <c r="BE100" s="93" t="n"/>
+      <c r="BF100" s="94" t="n"/>
+    </row>
+    <row r="101" ht="75" customHeight="1" s="92">
+      <c r="B101" s="42" t="n">
+        <v>97</v>
+      </c>
+      <c r="C101" s="93" t="n"/>
+      <c r="D101" s="94" t="n"/>
+      <c r="E101" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：类别就地修改（含其它/未归类）
+前置条件：训练集索引有数据
+操作步骤：1. 在类别下拉改类别
+2. 选「其它（other）」或「未归类（待处理）」</t>
+        </is>
+      </c>
+      <c r="F101" s="93" t="n"/>
+      <c r="G101" s="93" t="n"/>
+      <c r="H101" s="93" t="n"/>
+      <c r="I101" s="93" t="n"/>
+      <c r="J101" s="93" t="n"/>
+      <c r="K101" s="93" t="n"/>
+      <c r="L101" s="93" t="n"/>
+      <c r="M101" s="93" t="n"/>
+      <c r="N101" s="93" t="n"/>
+      <c r="O101" s="93" t="n"/>
+      <c r="P101" s="93" t="n"/>
+      <c r="Q101" s="93" t="n"/>
+      <c r="R101" s="93" t="n"/>
+      <c r="S101" s="93" t="n"/>
+      <c r="T101" s="93" t="n"/>
+      <c r="U101" s="94" t="n"/>
+      <c r="V101" s="52" t="inlineStr">
+        <is>
+          <t>修改即时生效并持久化；下拉包含 7 类 + 其它 + 未归类</t>
+        </is>
+      </c>
+      <c r="W101" s="93" t="n"/>
+      <c r="X101" s="93" t="n"/>
+      <c r="Y101" s="93" t="n"/>
+      <c r="Z101" s="93" t="n"/>
+      <c r="AA101" s="93" t="n"/>
+      <c r="AB101" s="93" t="n"/>
+      <c r="AC101" s="93" t="n"/>
+      <c r="AD101" s="93" t="n"/>
+      <c r="AE101" s="93" t="n"/>
+      <c r="AF101" s="93" t="n"/>
+      <c r="AG101" s="93" t="n"/>
+      <c r="AH101" s="93" t="n"/>
+      <c r="AI101" s="93" t="n"/>
+      <c r="AJ101" s="93" t="n"/>
+      <c r="AK101" s="93" t="n"/>
+      <c r="AL101" s="94" t="n"/>
+      <c r="AM101" s="101" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="AN101" s="93" t="n"/>
+      <c r="AO101" s="93" t="n"/>
+      <c r="AP101" s="94" t="n"/>
+      <c r="AQ101" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR101" s="93" t="n"/>
+      <c r="AS101" s="93" t="n"/>
+      <c r="AT101" s="94" t="n"/>
+      <c r="AU101" s="101" t="n"/>
+      <c r="AV101" s="93" t="n"/>
+      <c r="AW101" s="93" t="n"/>
+      <c r="AX101" s="94" t="n"/>
+      <c r="AY101" s="42" t="n"/>
+      <c r="AZ101" s="93" t="n"/>
+      <c r="BA101" s="93" t="n"/>
+      <c r="BB101" s="94" t="n"/>
+      <c r="BC101" s="101" t="inlineStr">
+        <is>
+          <t>见记录中心图4</t>
+        </is>
+      </c>
+      <c r="BD101" s="93" t="n"/>
+      <c r="BE101" s="93" t="n"/>
+      <c r="BF101" s="94" t="n"/>
+    </row>
+    <row r="102" ht="75" customHeight="1" s="92">
+      <c r="B102" s="42" t="n">
+        <v>98</v>
+      </c>
+      <c r="C102" s="93" t="n"/>
+      <c r="D102" s="94" t="n"/>
+      <c r="E102" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：划分下拉（train/val/test/未划分）
+前置条件：训练集索引有数据
+操作步骤：1. 单行改划分为 val
+2. 刷新核对</t>
+        </is>
+      </c>
+      <c r="F102" s="93" t="n"/>
+      <c r="G102" s="93" t="n"/>
+      <c r="H102" s="93" t="n"/>
+      <c r="I102" s="93" t="n"/>
+      <c r="J102" s="93" t="n"/>
+      <c r="K102" s="93" t="n"/>
+      <c r="L102" s="93" t="n"/>
+      <c r="M102" s="93" t="n"/>
+      <c r="N102" s="93" t="n"/>
+      <c r="O102" s="93" t="n"/>
+      <c r="P102" s="93" t="n"/>
+      <c r="Q102" s="93" t="n"/>
+      <c r="R102" s="93" t="n"/>
+      <c r="S102" s="93" t="n"/>
+      <c r="T102" s="93" t="n"/>
+      <c r="U102" s="94" t="n"/>
+      <c r="V102" s="52" t="inlineStr">
+        <is>
+          <t>划分值持久化，刷新后保持</t>
+        </is>
+      </c>
+      <c r="W102" s="93" t="n"/>
+      <c r="X102" s="93" t="n"/>
+      <c r="Y102" s="93" t="n"/>
+      <c r="Z102" s="93" t="n"/>
+      <c r="AA102" s="93" t="n"/>
+      <c r="AB102" s="93" t="n"/>
+      <c r="AC102" s="93" t="n"/>
+      <c r="AD102" s="93" t="n"/>
+      <c r="AE102" s="93" t="n"/>
+      <c r="AF102" s="93" t="n"/>
+      <c r="AG102" s="93" t="n"/>
+      <c r="AH102" s="93" t="n"/>
+      <c r="AI102" s="93" t="n"/>
+      <c r="AJ102" s="93" t="n"/>
+      <c r="AK102" s="93" t="n"/>
+      <c r="AL102" s="94" t="n"/>
+      <c r="AM102" s="101" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AN102" s="93" t="n"/>
+      <c r="AO102" s="93" t="n"/>
+      <c r="AP102" s="94" t="n"/>
+      <c r="AQ102" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR102" s="93" t="n"/>
+      <c r="AS102" s="93" t="n"/>
+      <c r="AT102" s="94" t="n"/>
+      <c r="AU102" s="101" t="n"/>
+      <c r="AV102" s="93" t="n"/>
+      <c r="AW102" s="93" t="n"/>
+      <c r="AX102" s="94" t="n"/>
+      <c r="AY102" s="42" t="n"/>
+      <c r="AZ102" s="93" t="n"/>
+      <c r="BA102" s="93" t="n"/>
+      <c r="BB102" s="94" t="n"/>
+      <c r="BC102" s="101" t="inlineStr">
+        <is>
+          <t>见记录中心图4</t>
+        </is>
+      </c>
+      <c r="BD102" s="93" t="n"/>
+      <c r="BE102" s="93" t="n"/>
+      <c r="BF102" s="94" t="n"/>
+    </row>
+    <row r="103" ht="75" customHeight="1" s="92">
+      <c r="B103" s="42" t="n">
+        <v>99</v>
+      </c>
+      <c r="C103" s="93" t="n"/>
+      <c r="D103" s="94" t="n"/>
+      <c r="E103" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：批量划分（勾选 + 8:2）
+前置条件：训练集索引有数据
+操作步骤：1. 勾选若干张（可跨页）
+2. 点击「按 8:2 划分」</t>
+        </is>
+      </c>
+      <c r="F103" s="93" t="n"/>
+      <c r="G103" s="93" t="n"/>
+      <c r="H103" s="93" t="n"/>
+      <c r="I103" s="93" t="n"/>
+      <c r="J103" s="93" t="n"/>
+      <c r="K103" s="93" t="n"/>
+      <c r="L103" s="93" t="n"/>
+      <c r="M103" s="93" t="n"/>
+      <c r="N103" s="93" t="n"/>
+      <c r="O103" s="93" t="n"/>
+      <c r="P103" s="93" t="n"/>
+      <c r="Q103" s="93" t="n"/>
+      <c r="R103" s="93" t="n"/>
+      <c r="S103" s="93" t="n"/>
+      <c r="T103" s="93" t="n"/>
+      <c r="U103" s="94" t="n"/>
+      <c r="V103" s="52" t="inlineStr">
+        <is>
+          <t>提示「已更新 N 张（train x / val y）」；勾选清空；列表划分列更新；未勾选时作用于当前筛选的全部图片</t>
+        </is>
+      </c>
+      <c r="W103" s="93" t="n"/>
+      <c r="X103" s="93" t="n"/>
+      <c r="Y103" s="93" t="n"/>
+      <c r="Z103" s="93" t="n"/>
+      <c r="AA103" s="93" t="n"/>
+      <c r="AB103" s="93" t="n"/>
+      <c r="AC103" s="93" t="n"/>
+      <c r="AD103" s="93" t="n"/>
+      <c r="AE103" s="93" t="n"/>
+      <c r="AF103" s="93" t="n"/>
+      <c r="AG103" s="93" t="n"/>
+      <c r="AH103" s="93" t="n"/>
+      <c r="AI103" s="93" t="n"/>
+      <c r="AJ103" s="93" t="n"/>
+      <c r="AK103" s="93" t="n"/>
+      <c r="AL103" s="94" t="n"/>
+      <c r="AM103" s="101" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="AN103" s="93" t="n"/>
+      <c r="AO103" s="93" t="n"/>
+      <c r="AP103" s="94" t="n"/>
+      <c r="AQ103" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR103" s="93" t="n"/>
+      <c r="AS103" s="93" t="n"/>
+      <c r="AT103" s="94" t="n"/>
+      <c r="AU103" s="101" t="n"/>
+      <c r="AV103" s="93" t="n"/>
+      <c r="AW103" s="93" t="n"/>
+      <c r="AX103" s="94" t="n"/>
+      <c r="AY103" s="42" t="n"/>
+      <c r="AZ103" s="93" t="n"/>
+      <c r="BA103" s="93" t="n"/>
+      <c r="BB103" s="94" t="n"/>
+      <c r="BC103" s="101" t="inlineStr">
+        <is>
+          <t>见记录中心图4</t>
+        </is>
+      </c>
+      <c r="BD103" s="93" t="n"/>
+      <c r="BE103" s="93" t="n"/>
+      <c r="BF103" s="94" t="n"/>
+    </row>
+    <row r="104" ht="75" customHeight="1" s="92">
+      <c r="B104" s="42" t="n">
+        <v>100</v>
+      </c>
+      <c r="C104" s="93" t="n"/>
+      <c r="D104" s="94" t="n"/>
+      <c r="E104" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：数据集筛选
+前置条件：训练集索引有数据
+操作步骤：1. 用类别 / 划分 / 标注 / 路径关键字筛选</t>
+        </is>
+      </c>
+      <c r="F104" s="93" t="n"/>
+      <c r="G104" s="93" t="n"/>
+      <c r="H104" s="93" t="n"/>
+      <c r="I104" s="93" t="n"/>
+      <c r="J104" s="93" t="n"/>
+      <c r="K104" s="93" t="n"/>
+      <c r="L104" s="93" t="n"/>
+      <c r="M104" s="93" t="n"/>
+      <c r="N104" s="93" t="n"/>
+      <c r="O104" s="93" t="n"/>
+      <c r="P104" s="93" t="n"/>
+      <c r="Q104" s="93" t="n"/>
+      <c r="R104" s="93" t="n"/>
+      <c r="S104" s="93" t="n"/>
+      <c r="T104" s="93" t="n"/>
+      <c r="U104" s="94" t="n"/>
+      <c r="V104" s="52" t="inlineStr">
+        <is>
+          <t>结果与条件一致；清零后恢复全部；分页总数同步</t>
+        </is>
+      </c>
+      <c r="W104" s="93" t="n"/>
+      <c r="X104" s="93" t="n"/>
+      <c r="Y104" s="93" t="n"/>
+      <c r="Z104" s="93" t="n"/>
+      <c r="AA104" s="93" t="n"/>
+      <c r="AB104" s="93" t="n"/>
+      <c r="AC104" s="93" t="n"/>
+      <c r="AD104" s="93" t="n"/>
+      <c r="AE104" s="93" t="n"/>
+      <c r="AF104" s="93" t="n"/>
+      <c r="AG104" s="93" t="n"/>
+      <c r="AH104" s="93" t="n"/>
+      <c r="AI104" s="93" t="n"/>
+      <c r="AJ104" s="93" t="n"/>
+      <c r="AK104" s="93" t="n"/>
+      <c r="AL104" s="94" t="n"/>
+      <c r="AM104" s="101" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="AN104" s="93" t="n"/>
+      <c r="AO104" s="93" t="n"/>
+      <c r="AP104" s="94" t="n"/>
+      <c r="AQ104" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR104" s="93" t="n"/>
+      <c r="AS104" s="93" t="n"/>
+      <c r="AT104" s="94" t="n"/>
+      <c r="AU104" s="101" t="n"/>
+      <c r="AV104" s="93" t="n"/>
+      <c r="AW104" s="93" t="n"/>
+      <c r="AX104" s="94" t="n"/>
+      <c r="AY104" s="42" t="n"/>
+      <c r="AZ104" s="93" t="n"/>
+      <c r="BA104" s="93" t="n"/>
+      <c r="BB104" s="94" t="n"/>
+      <c r="BC104" s="101" t="inlineStr">
+        <is>
+          <t>见记录中心图4</t>
+        </is>
+      </c>
+      <c r="BD104" s="93" t="n"/>
+      <c r="BE104" s="93" t="n"/>
+      <c r="BF104" s="94" t="n"/>
+    </row>
+    <row r="105" ht="75" customHeight="1" s="92">
+      <c r="B105" s="42" t="n">
+        <v>101</v>
+      </c>
+      <c r="C105" s="93" t="n"/>
+      <c r="D105" s="94" t="n"/>
+      <c r="E105" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：回填历史抓拍
+前置条件：training/captures 有历史图片
+操作步骤：1. 点击「回填历史抓拍」
+2. 观察提示与索引总数</t>
+        </is>
+      </c>
+      <c r="F105" s="93" t="n"/>
+      <c r="G105" s="93" t="n"/>
+      <c r="H105" s="93" t="n"/>
+      <c r="I105" s="93" t="n"/>
+      <c r="J105" s="93" t="n"/>
+      <c r="K105" s="93" t="n"/>
+      <c r="L105" s="93" t="n"/>
+      <c r="M105" s="93" t="n"/>
+      <c r="N105" s="93" t="n"/>
+      <c r="O105" s="93" t="n"/>
+      <c r="P105" s="93" t="n"/>
+      <c r="Q105" s="93" t="n"/>
+      <c r="R105" s="93" t="n"/>
+      <c r="S105" s="93" t="n"/>
+      <c r="T105" s="93" t="n"/>
+      <c r="U105" s="94" t="n"/>
+      <c r="V105" s="52" t="inlineStr">
+        <is>
+          <t>提示扫描/新增/更新/跳过数量；索引总数增加；**再次点击新增为 0**（幂等）；根目录无法判定类别的图片被跳过</t>
+        </is>
+      </c>
+      <c r="W105" s="93" t="n"/>
+      <c r="X105" s="93" t="n"/>
+      <c r="Y105" s="93" t="n"/>
+      <c r="Z105" s="93" t="n"/>
+      <c r="AA105" s="93" t="n"/>
+      <c r="AB105" s="93" t="n"/>
+      <c r="AC105" s="93" t="n"/>
+      <c r="AD105" s="93" t="n"/>
+      <c r="AE105" s="93" t="n"/>
+      <c r="AF105" s="93" t="n"/>
+      <c r="AG105" s="93" t="n"/>
+      <c r="AH105" s="93" t="n"/>
+      <c r="AI105" s="93" t="n"/>
+      <c r="AJ105" s="93" t="n"/>
+      <c r="AK105" s="93" t="n"/>
+      <c r="AL105" s="94" t="n"/>
+      <c r="AM105" s="101" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AN105" s="93" t="n"/>
+      <c r="AO105" s="93" t="n"/>
+      <c r="AP105" s="94" t="n"/>
+      <c r="AQ105" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR105" s="93" t="n"/>
+      <c r="AS105" s="93" t="n"/>
+      <c r="AT105" s="94" t="n"/>
+      <c r="AU105" s="101" t="n"/>
+      <c r="AV105" s="93" t="n"/>
+      <c r="AW105" s="93" t="n"/>
+      <c r="AX105" s="94" t="n"/>
+      <c r="AY105" s="42" t="n"/>
+      <c r="AZ105" s="93" t="n"/>
+      <c r="BA105" s="93" t="n"/>
+      <c r="BB105" s="94" t="n"/>
+      <c r="BC105" s="101" t="inlineStr">
+        <is>
+          <t>见记录中心图4</t>
+        </is>
+      </c>
+      <c r="BD105" s="93" t="n"/>
+      <c r="BE105" s="93" t="n"/>
+      <c r="BF105" s="94" t="n"/>
+    </row>
+    <row r="106" ht="75" customHeight="1" s="92">
+      <c r="B106" s="42" t="n">
+        <v>102</v>
+      </c>
+      <c r="C106" s="93" t="n"/>
+      <c r="D106" s="94" t="n"/>
+      <c r="E106" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：导出 CSV
+前置条件：已有记录
+操作步骤：1. 点击「导出 CSV」
+2. 用 Excel 打开</t>
+        </is>
+      </c>
+      <c r="F106" s="93" t="n"/>
+      <c r="G106" s="93" t="n"/>
+      <c r="H106" s="93" t="n"/>
+      <c r="I106" s="93" t="n"/>
+      <c r="J106" s="93" t="n"/>
+      <c r="K106" s="93" t="n"/>
+      <c r="L106" s="93" t="n"/>
+      <c r="M106" s="93" t="n"/>
+      <c r="N106" s="93" t="n"/>
+      <c r="O106" s="93" t="n"/>
+      <c r="P106" s="93" t="n"/>
+      <c r="Q106" s="93" t="n"/>
+      <c r="R106" s="93" t="n"/>
+      <c r="S106" s="93" t="n"/>
+      <c r="T106" s="93" t="n"/>
+      <c r="U106" s="94" t="n"/>
+      <c r="V106" s="52" t="inlineStr">
+        <is>
+          <t>下载成功；中文不乱码（含 BOM）；判定与训练集标记反映真实状态</t>
+        </is>
+      </c>
+      <c r="W106" s="93" t="n"/>
+      <c r="X106" s="93" t="n"/>
+      <c r="Y106" s="93" t="n"/>
+      <c r="Z106" s="93" t="n"/>
+      <c r="AA106" s="93" t="n"/>
+      <c r="AB106" s="93" t="n"/>
+      <c r="AC106" s="93" t="n"/>
+      <c r="AD106" s="93" t="n"/>
+      <c r="AE106" s="93" t="n"/>
+      <c r="AF106" s="93" t="n"/>
+      <c r="AG106" s="93" t="n"/>
+      <c r="AH106" s="93" t="n"/>
+      <c r="AI106" s="93" t="n"/>
+      <c r="AJ106" s="93" t="n"/>
+      <c r="AK106" s="93" t="n"/>
+      <c r="AL106" s="94" t="n"/>
+      <c r="AM106" s="101" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AN106" s="93" t="n"/>
+      <c r="AO106" s="93" t="n"/>
+      <c r="AP106" s="94" t="n"/>
+      <c r="AQ106" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR106" s="93" t="n"/>
+      <c r="AS106" s="93" t="n"/>
+      <c r="AT106" s="94" t="n"/>
+      <c r="AU106" s="101" t="n"/>
+      <c r="AV106" s="93" t="n"/>
+      <c r="AW106" s="93" t="n"/>
+      <c r="AX106" s="94" t="n"/>
+      <c r="AY106" s="42" t="n"/>
+      <c r="AZ106" s="93" t="n"/>
+      <c r="BA106" s="93" t="n"/>
+      <c r="BB106" s="94" t="n"/>
+      <c r="BC106" s="101" t="inlineStr">
+        <is>
+          <t>见记录中心图5</t>
+        </is>
+      </c>
+      <c r="BD106" s="93" t="n"/>
+      <c r="BE106" s="93" t="n"/>
+      <c r="BF106" s="94" t="n"/>
+    </row>
+    <row r="107" ht="75" customHeight="1" s="92">
+      <c r="B107" s="42" t="n">
+        <v>103</v>
+      </c>
+      <c r="C107" s="93" t="n"/>
+      <c r="D107" s="94" t="n"/>
+      <c r="E107" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：标注页按类别筛选
+前置条件：数据标注页已加载图片
+操作步骤：1. 在「全部/未标注/已标注」之下的类别下拉中选择某类别
+2. 再叠加切换状态筛选</t>
+        </is>
+      </c>
+      <c r="F107" s="93" t="n"/>
+      <c r="G107" s="93" t="n"/>
+      <c r="H107" s="93" t="n"/>
+      <c r="I107" s="93" t="n"/>
+      <c r="J107" s="93" t="n"/>
+      <c r="K107" s="93" t="n"/>
+      <c r="L107" s="93" t="n"/>
+      <c r="M107" s="93" t="n"/>
+      <c r="N107" s="93" t="n"/>
+      <c r="O107" s="93" t="n"/>
+      <c r="P107" s="93" t="n"/>
+      <c r="Q107" s="93" t="n"/>
+      <c r="R107" s="93" t="n"/>
+      <c r="S107" s="93" t="n"/>
+      <c r="T107" s="93" t="n"/>
+      <c r="U107" s="94" t="n"/>
+      <c r="V107" s="52" t="inlineStr">
+        <is>
+          <t>列表只显示该类别图片；下拉项显示各类别数量（如 paper（576 张））；清空回到全部；类别少于 2 个时下拉自动隐藏</t>
+        </is>
+      </c>
+      <c r="W107" s="93" t="n"/>
+      <c r="X107" s="93" t="n"/>
+      <c r="Y107" s="93" t="n"/>
+      <c r="Z107" s="93" t="n"/>
+      <c r="AA107" s="93" t="n"/>
+      <c r="AB107" s="93" t="n"/>
+      <c r="AC107" s="93" t="n"/>
+      <c r="AD107" s="93" t="n"/>
+      <c r="AE107" s="93" t="n"/>
+      <c r="AF107" s="93" t="n"/>
+      <c r="AG107" s="93" t="n"/>
+      <c r="AH107" s="93" t="n"/>
+      <c r="AI107" s="93" t="n"/>
+      <c r="AJ107" s="93" t="n"/>
+      <c r="AK107" s="93" t="n"/>
+      <c r="AL107" s="94" t="n"/>
+      <c r="AM107" s="101" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="AN107" s="93" t="n"/>
+      <c r="AO107" s="93" t="n"/>
+      <c r="AP107" s="94" t="n"/>
+      <c r="AQ107" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR107" s="93" t="n"/>
+      <c r="AS107" s="93" t="n"/>
+      <c r="AT107" s="94" t="n"/>
+      <c r="AU107" s="101" t="n"/>
+      <c r="AV107" s="93" t="n"/>
+      <c r="AW107" s="93" t="n"/>
+      <c r="AX107" s="94" t="n"/>
+      <c r="AY107" s="42" t="n"/>
+      <c r="AZ107" s="93" t="n"/>
+      <c r="BA107" s="93" t="n"/>
+      <c r="BB107" s="94" t="n"/>
+      <c r="BC107" s="101" t="inlineStr">
+        <is>
+          <t>见 UI 界面（标注页截图）</t>
+        </is>
+      </c>
+      <c r="BD107" s="93" t="n"/>
+      <c r="BE107" s="93" t="n"/>
+      <c r="BF107" s="94" t="n"/>
+    </row>
+    <row r="108" ht="75" customHeight="1" s="92">
+      <c r="B108" s="42" t="n">
+        <v>104</v>
+      </c>
+      <c r="C108" s="93" t="n"/>
+      <c r="D108" s="94" t="n"/>
+      <c r="E108" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：每次下发产生一条记录
+前置条件：摄像头与模型就绪（串口可选）
+操作步骤：1. 触发一次下发（自动识别或手动）
+2. 查看记录中心与数据库</t>
+        </is>
+      </c>
+      <c r="F108" s="93" t="n"/>
+      <c r="G108" s="93" t="n"/>
+      <c r="H108" s="93" t="n"/>
+      <c r="I108" s="93" t="n"/>
+      <c r="J108" s="93" t="n"/>
+      <c r="K108" s="93" t="n"/>
+      <c r="L108" s="93" t="n"/>
+      <c r="M108" s="93" t="n"/>
+      <c r="N108" s="93" t="n"/>
+      <c r="O108" s="93" t="n"/>
+      <c r="P108" s="93" t="n"/>
+      <c r="Q108" s="93" t="n"/>
+      <c r="R108" s="93" t="n"/>
+      <c r="S108" s="93" t="n"/>
+      <c r="T108" s="93" t="n"/>
+      <c r="U108" s="94" t="n"/>
+      <c r="V108" s="52" t="inlineStr">
+        <is>
+          <t>新增一条记录：类别/置信度/桶位/角度/串口结果/来源齐全；同时写入三张图（原始/带框/缩略图）</t>
+        </is>
+      </c>
+      <c r="W108" s="93" t="n"/>
+      <c r="X108" s="93" t="n"/>
+      <c r="Y108" s="93" t="n"/>
+      <c r="Z108" s="93" t="n"/>
+      <c r="AA108" s="93" t="n"/>
+      <c r="AB108" s="93" t="n"/>
+      <c r="AC108" s="93" t="n"/>
+      <c r="AD108" s="93" t="n"/>
+      <c r="AE108" s="93" t="n"/>
+      <c r="AF108" s="93" t="n"/>
+      <c r="AG108" s="93" t="n"/>
+      <c r="AH108" s="93" t="n"/>
+      <c r="AI108" s="93" t="n"/>
+      <c r="AJ108" s="93" t="n"/>
+      <c r="AK108" s="93" t="n"/>
+      <c r="AL108" s="94" t="n"/>
+      <c r="AM108" s="101" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AN108" s="93" t="n"/>
+      <c r="AO108" s="93" t="n"/>
+      <c r="AP108" s="94" t="n"/>
+      <c r="AQ108" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR108" s="93" t="n"/>
+      <c r="AS108" s="93" t="n"/>
+      <c r="AT108" s="94" t="n"/>
+      <c r="AU108" s="101" t="n"/>
+      <c r="AV108" s="93" t="n"/>
+      <c r="AW108" s="93" t="n"/>
+      <c r="AX108" s="94" t="n"/>
+      <c r="AY108" s="42" t="n"/>
+      <c r="AZ108" s="93" t="n"/>
+      <c r="BA108" s="93" t="n"/>
+      <c r="BB108" s="94" t="n"/>
+      <c r="BC108" s="101" t="inlineStr">
+        <is>
+          <t>见运行图10</t>
+        </is>
+      </c>
+      <c r="BD108" s="93" t="n"/>
+      <c r="BE108" s="93" t="n"/>
+      <c r="BF108" s="94" t="n"/>
+    </row>
+    <row r="109" ht="75" customHeight="1" s="92">
+      <c r="B109" s="42" t="n">
+        <v>105</v>
+      </c>
+      <c r="C109" s="93" t="n"/>
+      <c r="D109" s="94" t="n"/>
+      <c r="E109" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：记录三尺寸图片接口
+前置条件：已有记录图片
+操作步骤：1. 依次请求 thumb / marked / raw</t>
+        </is>
+      </c>
+      <c r="F109" s="93" t="n"/>
+      <c r="G109" s="93" t="n"/>
+      <c r="H109" s="93" t="n"/>
+      <c r="I109" s="93" t="n"/>
+      <c r="J109" s="93" t="n"/>
+      <c r="K109" s="93" t="n"/>
+      <c r="L109" s="93" t="n"/>
+      <c r="M109" s="93" t="n"/>
+      <c r="N109" s="93" t="n"/>
+      <c r="O109" s="93" t="n"/>
+      <c r="P109" s="93" t="n"/>
+      <c r="Q109" s="93" t="n"/>
+      <c r="R109" s="93" t="n"/>
+      <c r="S109" s="93" t="n"/>
+      <c r="T109" s="93" t="n"/>
+      <c r="U109" s="94" t="n"/>
+      <c r="V109" s="52" t="inlineStr">
+        <is>
+          <t>三者均可访问：thumb 最小（列表用）、marked 带检测框、raw 为原始无框帧；带一天缓存头</t>
+        </is>
+      </c>
+      <c r="W109" s="93" t="n"/>
+      <c r="X109" s="93" t="n"/>
+      <c r="Y109" s="93" t="n"/>
+      <c r="Z109" s="93" t="n"/>
+      <c r="AA109" s="93" t="n"/>
+      <c r="AB109" s="93" t="n"/>
+      <c r="AC109" s="93" t="n"/>
+      <c r="AD109" s="93" t="n"/>
+      <c r="AE109" s="93" t="n"/>
+      <c r="AF109" s="93" t="n"/>
+      <c r="AG109" s="93" t="n"/>
+      <c r="AH109" s="93" t="n"/>
+      <c r="AI109" s="93" t="n"/>
+      <c r="AJ109" s="93" t="n"/>
+      <c r="AK109" s="93" t="n"/>
+      <c r="AL109" s="94" t="n"/>
+      <c r="AM109" s="101" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AN109" s="93" t="n"/>
+      <c r="AO109" s="93" t="n"/>
+      <c r="AP109" s="94" t="n"/>
+      <c r="AQ109" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR109" s="93" t="n"/>
+      <c r="AS109" s="93" t="n"/>
+      <c r="AT109" s="94" t="n"/>
+      <c r="AU109" s="101" t="n"/>
+      <c r="AV109" s="93" t="n"/>
+      <c r="AW109" s="93" t="n"/>
+      <c r="AX109" s="94" t="n"/>
+      <c r="AY109" s="42" t="n"/>
+      <c r="AZ109" s="93" t="n"/>
+      <c r="BA109" s="93" t="n"/>
+      <c r="BB109" s="94" t="n"/>
+      <c r="BC109" s="101" t="inlineStr">
+        <is>
+          <t>见运行图10</t>
+        </is>
+      </c>
+      <c r="BD109" s="93" t="n"/>
+      <c r="BE109" s="93" t="n"/>
+      <c r="BF109" s="94" t="n"/>
+    </row>
+    <row r="110" ht="75" customHeight="1" s="92">
+      <c r="B110" s="42" t="n">
+        <v>106</v>
+      </c>
+      <c r="C110" s="93" t="n"/>
+      <c r="D110" s="94" t="n"/>
+      <c r="E110" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：数据库不可用时的降级
+前置条件：把数据库连接串改错后启动
+操作步骤：1. 启动后端
+2. 打开记录中心</t>
+        </is>
+      </c>
+      <c r="F110" s="93" t="n"/>
+      <c r="G110" s="93" t="n"/>
+      <c r="H110" s="93" t="n"/>
+      <c r="I110" s="93" t="n"/>
+      <c r="J110" s="93" t="n"/>
+      <c r="K110" s="93" t="n"/>
+      <c r="L110" s="93" t="n"/>
+      <c r="M110" s="93" t="n"/>
+      <c r="N110" s="93" t="n"/>
+      <c r="O110" s="93" t="n"/>
+      <c r="P110" s="93" t="n"/>
+      <c r="Q110" s="93" t="n"/>
+      <c r="R110" s="93" t="n"/>
+      <c r="S110" s="93" t="n"/>
+      <c r="T110" s="93" t="n"/>
+      <c r="U110" s="94" t="n"/>
+      <c r="V110" s="52" t="inlineStr">
+        <is>
+          <t>主流程照常（摄像头/检测/串口可用）；记录接口返回 503 并提示「数据库未连接」；界面不崩、无白屏</t>
+        </is>
+      </c>
+      <c r="W110" s="93" t="n"/>
+      <c r="X110" s="93" t="n"/>
+      <c r="Y110" s="93" t="n"/>
+      <c r="Z110" s="93" t="n"/>
+      <c r="AA110" s="93" t="n"/>
+      <c r="AB110" s="93" t="n"/>
+      <c r="AC110" s="93" t="n"/>
+      <c r="AD110" s="93" t="n"/>
+      <c r="AE110" s="93" t="n"/>
+      <c r="AF110" s="93" t="n"/>
+      <c r="AG110" s="93" t="n"/>
+      <c r="AH110" s="93" t="n"/>
+      <c r="AI110" s="93" t="n"/>
+      <c r="AJ110" s="93" t="n"/>
+      <c r="AK110" s="93" t="n"/>
+      <c r="AL110" s="94" t="n"/>
+      <c r="AM110" s="101" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="AN110" s="93" t="n"/>
+      <c r="AO110" s="93" t="n"/>
+      <c r="AP110" s="94" t="n"/>
+      <c r="AQ110" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR110" s="93" t="n"/>
+      <c r="AS110" s="93" t="n"/>
+      <c r="AT110" s="94" t="n"/>
+      <c r="AU110" s="101" t="n"/>
+      <c r="AV110" s="93" t="n"/>
+      <c r="AW110" s="93" t="n"/>
+      <c r="AX110" s="94" t="n"/>
+      <c r="AY110" s="42" t="n"/>
+      <c r="AZ110" s="93" t="n"/>
+      <c r="BA110" s="93" t="n"/>
+      <c r="BB110" s="94" t="n"/>
+      <c r="BC110" s="101" t="inlineStr">
+        <is>
+          <t>见运行图11</t>
+        </is>
+      </c>
+      <c r="BD110" s="93" t="n"/>
+      <c r="BE110" s="93" t="n"/>
+      <c r="BF110" s="94" t="n"/>
+    </row>
+    <row r="111" ht="75" customHeight="1" s="92">
+      <c r="B111" s="42" t="n">
+        <v>107</v>
+      </c>
+      <c r="C111" s="93" t="n"/>
+      <c r="D111" s="94" t="n"/>
+      <c r="E111" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：库体积监控与保留清理
+前置条件：已有若干记录
+操作步骤：1. 查看 /api/db/status 的 size_bytes
+2. 调用 /api/records-cleanup?days=30&amp;dry_run=true</t>
+        </is>
+      </c>
+      <c r="F111" s="93" t="n"/>
+      <c r="G111" s="93" t="n"/>
+      <c r="H111" s="93" t="n"/>
+      <c r="I111" s="93" t="n"/>
+      <c r="J111" s="93" t="n"/>
+      <c r="K111" s="93" t="n"/>
+      <c r="L111" s="93" t="n"/>
+      <c r="M111" s="93" t="n"/>
+      <c r="N111" s="93" t="n"/>
+      <c r="O111" s="93" t="n"/>
+      <c r="P111" s="93" t="n"/>
+      <c r="Q111" s="93" t="n"/>
+      <c r="R111" s="93" t="n"/>
+      <c r="S111" s="93" t="n"/>
+      <c r="T111" s="93" t="n"/>
+      <c r="U111" s="94" t="n"/>
+      <c r="V111" s="52" t="inlineStr">
+        <is>
+          <t>返回库体积（KB/MB）与将删除条数；真实清理后记录与图片消失、库体积下降；后台每 6 小时自动清理一次</t>
+        </is>
+      </c>
+      <c r="W111" s="93" t="n"/>
+      <c r="X111" s="93" t="n"/>
+      <c r="Y111" s="93" t="n"/>
+      <c r="Z111" s="93" t="n"/>
+      <c r="AA111" s="93" t="n"/>
+      <c r="AB111" s="93" t="n"/>
+      <c r="AC111" s="93" t="n"/>
+      <c r="AD111" s="93" t="n"/>
+      <c r="AE111" s="93" t="n"/>
+      <c r="AF111" s="93" t="n"/>
+      <c r="AG111" s="93" t="n"/>
+      <c r="AH111" s="93" t="n"/>
+      <c r="AI111" s="93" t="n"/>
+      <c r="AJ111" s="93" t="n"/>
+      <c r="AK111" s="93" t="n"/>
+      <c r="AL111" s="94" t="n"/>
+      <c r="AM111" s="101" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="AN111" s="93" t="n"/>
+      <c r="AO111" s="93" t="n"/>
+      <c r="AP111" s="94" t="n"/>
+      <c r="AQ111" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR111" s="93" t="n"/>
+      <c r="AS111" s="93" t="n"/>
+      <c r="AT111" s="94" t="n"/>
+      <c r="AU111" s="101" t="n"/>
+      <c r="AV111" s="93" t="n"/>
+      <c r="AW111" s="93" t="n"/>
+      <c r="AX111" s="94" t="n"/>
+      <c r="AY111" s="42" t="n"/>
+      <c r="AZ111" s="93" t="n"/>
+      <c r="BA111" s="93" t="n"/>
+      <c r="BB111" s="94" t="n"/>
+      <c r="BC111" s="101" t="inlineStr">
+        <is>
+          <t>见运行图11</t>
+        </is>
+      </c>
+      <c r="BD111" s="93" t="n"/>
+      <c r="BE111" s="93" t="n"/>
+      <c r="BF111" s="94" t="n"/>
+    </row>
+    <row r="112" ht="75" customHeight="1" s="92">
+      <c r="B112" s="42" t="n">
+        <v>108</v>
+      </c>
+      <c r="C112" s="93" t="n"/>
+      <c r="D112" s="94" t="n"/>
+      <c r="E112" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：记录功能不影响检测帧率
+前置条件：检测运行中且记录开启
+操作步骤：1. 连续触发 10 次下发
+2. 观察推理 FPS 与单帧耗时</t>
+        </is>
+      </c>
+      <c r="F112" s="93" t="n"/>
+      <c r="G112" s="93" t="n"/>
+      <c r="H112" s="93" t="n"/>
+      <c r="I112" s="93" t="n"/>
+      <c r="J112" s="93" t="n"/>
+      <c r="K112" s="93" t="n"/>
+      <c r="L112" s="93" t="n"/>
+      <c r="M112" s="93" t="n"/>
+      <c r="N112" s="93" t="n"/>
+      <c r="O112" s="93" t="n"/>
+      <c r="P112" s="93" t="n"/>
+      <c r="Q112" s="93" t="n"/>
+      <c r="R112" s="93" t="n"/>
+      <c r="S112" s="93" t="n"/>
+      <c r="T112" s="93" t="n"/>
+      <c r="U112" s="94" t="n"/>
+      <c r="V112" s="52" t="inlineStr">
+        <is>
+          <t>FPS 与单帧耗时无明显劣化（记录在独立线程，队列满则丢弃并计数）</t>
+        </is>
+      </c>
+      <c r="W112" s="93" t="n"/>
+      <c r="X112" s="93" t="n"/>
+      <c r="Y112" s="93" t="n"/>
+      <c r="Z112" s="93" t="n"/>
+      <c r="AA112" s="93" t="n"/>
+      <c r="AB112" s="93" t="n"/>
+      <c r="AC112" s="93" t="n"/>
+      <c r="AD112" s="93" t="n"/>
+      <c r="AE112" s="93" t="n"/>
+      <c r="AF112" s="93" t="n"/>
+      <c r="AG112" s="93" t="n"/>
+      <c r="AH112" s="93" t="n"/>
+      <c r="AI112" s="93" t="n"/>
+      <c r="AJ112" s="93" t="n"/>
+      <c r="AK112" s="93" t="n"/>
+      <c r="AL112" s="94" t="n"/>
+      <c r="AM112" s="101" t="inlineStr">
+        <is>
+          <t>待执行</t>
+        </is>
+      </c>
+      <c r="AN112" s="93" t="n"/>
+      <c r="AO112" s="93" t="n"/>
+      <c r="AP112" s="94" t="n"/>
+      <c r="AQ112" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR112" s="93" t="n"/>
+      <c r="AS112" s="93" t="n"/>
+      <c r="AT112" s="94" t="n"/>
+      <c r="AU112" s="101" t="n"/>
+      <c r="AV112" s="93" t="n"/>
+      <c r="AW112" s="93" t="n"/>
+      <c r="AX112" s="94" t="n"/>
+      <c r="AY112" s="42" t="n"/>
+      <c r="AZ112" s="93" t="n"/>
+      <c r="BA112" s="93" t="n"/>
+      <c r="BB112" s="94" t="n"/>
+      <c r="BC112" s="101" t="inlineStr">
+        <is>
+          <t>见运行图10</t>
+        </is>
+      </c>
+      <c r="BD112" s="93" t="n"/>
+      <c r="BE112" s="93" t="n"/>
+      <c r="BF112" s="94" t="n"/>
+    </row>
+    <row r="113" ht="75" customHeight="1" s="92">
+      <c r="B113" s="42" t="n">
+        <v>109</v>
+      </c>
+      <c r="C113" s="93" t="n"/>
+      <c r="D113" s="94" t="n"/>
+      <c r="E113" s="52" t="inlineStr">
+        <is>
+          <t>用例标题：人工判定后回流训练集闭环
+前置条件：记录已判定为错误并纠正类别
+操作步骤：1. 点击「入训练集」
+2. 检查 training/captures/&lt;真实类别&gt;/ 与索引</t>
+        </is>
+      </c>
+      <c r="F113" s="93" t="n"/>
+      <c r="G113" s="93" t="n"/>
+      <c r="H113" s="93" t="n"/>
+      <c r="I113" s="93" t="n"/>
+      <c r="J113" s="93" t="n"/>
+      <c r="K113" s="93" t="n"/>
+      <c r="L113" s="93" t="n"/>
+      <c r="M113" s="93" t="n"/>
+      <c r="N113" s="93" t="n"/>
+      <c r="O113" s="93" t="n"/>
+      <c r="P113" s="93" t="n"/>
+      <c r="Q113" s="93" t="n"/>
+      <c r="R113" s="93" t="n"/>
+      <c r="S113" s="93" t="n"/>
+      <c r="T113" s="93" t="n"/>
+      <c r="U113" s="94" t="n"/>
+      <c r="V113" s="52" t="inlineStr">
+        <is>
+          <t>图片按**真实类别**归档（不是模型预测类别）；索引记录 predicted 与 true_class 可对比；可用于下一轮训练</t>
+        </is>
+      </c>
+      <c r="W113" s="93" t="n"/>
+      <c r="X113" s="93" t="n"/>
+      <c r="Y113" s="93" t="n"/>
+      <c r="Z113" s="93" t="n"/>
+      <c r="AA113" s="93" t="n"/>
+      <c r="AB113" s="93" t="n"/>
+      <c r="AC113" s="93" t="n"/>
+      <c r="AD113" s="93" t="n"/>
+      <c r="AE113" s="93" t="n"/>
+      <c r="AF113" s="93" t="n"/>
+      <c r="AG113" s="93" t="n"/>
+      <c r="AH113" s="93" t="n"/>
+      <c r="AI113" s="93" t="n"/>
+      <c r="AJ113" s="93" t="n"/>
+      <c r="AK113" s="93" t="n"/>
+      <c r="AL113" s="94" t="n"/>
+      <c r="AM113" s="101" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AN113" s="93" t="n"/>
+      <c r="AO113" s="93" t="n"/>
+      <c r="AP113" s="94" t="n"/>
+      <c r="AQ113" s="102" t="n">
+        <v>46321</v>
+      </c>
+      <c r="AR113" s="93" t="n"/>
+      <c r="AS113" s="93" t="n"/>
+      <c r="AT113" s="94" t="n"/>
+      <c r="AU113" s="101" t="n"/>
+      <c r="AV113" s="93" t="n"/>
+      <c r="AW113" s="93" t="n"/>
+      <c r="AX113" s="94" t="n"/>
+      <c r="AY113" s="42" t="n"/>
+      <c r="AZ113" s="93" t="n"/>
+      <c r="BA113" s="93" t="n"/>
+      <c r="BB113" s="94" t="n"/>
+      <c r="BC113" s="101" t="inlineStr">
+        <is>
+          <t>见运行图10</t>
+        </is>
+      </c>
+      <c r="BD113" s="93" t="n"/>
+      <c r="BE113" s="93" t="n"/>
+      <c r="BF113" s="94" t="n"/>
+    </row>
     <row r="114" ht="20.25" customHeight="1" s="92"/>
     <row r="115" ht="20.25" customHeight="1" s="92"/>
     <row r="116" ht="20.25" customHeight="1" s="92"/>
@@ -10585,11 +12523,13 @@
     <row r="187" ht="20.25" customHeight="1" s="92"/>
     <row r="188" ht="20.25" customHeight="1" s="92"/>
   </sheetData>
-  <mergeCells count="696">
+  <mergeCells count="888">
     <mergeCell ref="AY29:BB29"/>
     <mergeCell ref="B60:D60"/>
+    <mergeCell ref="AY94:BB94"/>
     <mergeCell ref="E18:U18"/>
     <mergeCell ref="V21:AL21"/>
+    <mergeCell ref="V92:AL92"/>
     <mergeCell ref="AQ9:AT9"/>
     <mergeCell ref="AQ69:AT69"/>
     <mergeCell ref="BC20:BF20"/>
@@ -10599,11 +12539,17 @@
     <mergeCell ref="AM55:AP55"/>
     <mergeCell ref="BC38:BF38"/>
     <mergeCell ref="AY6:BB6"/>
+    <mergeCell ref="BC109:BF109"/>
+    <mergeCell ref="AU112:AX112"/>
     <mergeCell ref="V23:AL23"/>
     <mergeCell ref="AQ6:AT6"/>
+    <mergeCell ref="V94:AL94"/>
     <mergeCell ref="BC84:BF84"/>
     <mergeCell ref="AU62:AX62"/>
+    <mergeCell ref="E92:U92"/>
+    <mergeCell ref="AQ98:AT98"/>
     <mergeCell ref="AY89:BB89"/>
+    <mergeCell ref="AU100:AX100"/>
     <mergeCell ref="B84:D84"/>
     <mergeCell ref="V87:AL87"/>
     <mergeCell ref="AM42:AP42"/>
@@ -10614,6 +12560,7 @@
     <mergeCell ref="BC80:BF80"/>
     <mergeCell ref="BC51:BF51"/>
     <mergeCell ref="AM23:AP23"/>
+    <mergeCell ref="E94:U94"/>
     <mergeCell ref="V24:AL24"/>
     <mergeCell ref="E69:U69"/>
     <mergeCell ref="B80:D80"/>
@@ -10637,6 +12584,8 @@
     <mergeCell ref="AY19:BB19"/>
     <mergeCell ref="BC43:BF43"/>
     <mergeCell ref="AU57:AX57"/>
+    <mergeCell ref="AQ93:AT93"/>
+    <mergeCell ref="AU113:AX113"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="V17:AL17"/>
     <mergeCell ref="V55:AL55"/>
@@ -10648,37 +12597,49 @@
     <mergeCell ref="BC34:BF34"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="BC28:BF28"/>
+    <mergeCell ref="AU102:AX102"/>
     <mergeCell ref="AM80:AP80"/>
     <mergeCell ref="E17:U17"/>
     <mergeCell ref="E88:U88"/>
+    <mergeCell ref="V111:AL111"/>
+    <mergeCell ref="B99:D99"/>
     <mergeCell ref="AU52:AX52"/>
     <mergeCell ref="E82:U82"/>
     <mergeCell ref="V29:AL29"/>
     <mergeCell ref="AY3:BB3"/>
     <mergeCell ref="AU39:AX39"/>
     <mergeCell ref="B74:D74"/>
+    <mergeCell ref="AY108:BB108"/>
     <mergeCell ref="B68:D68"/>
     <mergeCell ref="BC59:BF59"/>
+    <mergeCell ref="AY95:BB95"/>
     <mergeCell ref="E19:U19"/>
     <mergeCell ref="V44:AL44"/>
     <mergeCell ref="AM46:AP46"/>
     <mergeCell ref="V31:AL31"/>
+    <mergeCell ref="AU103:AX103"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B76:D76"/>
     <mergeCell ref="AY32:BB32"/>
     <mergeCell ref="AU4:AX4"/>
     <mergeCell ref="BC61:BF61"/>
     <mergeCell ref="AQ37:AT37"/>
+    <mergeCell ref="AY97:BB97"/>
+    <mergeCell ref="V108:AL108"/>
+    <mergeCell ref="AY109:BB109"/>
     <mergeCell ref="AY72:BB72"/>
     <mergeCell ref="AQ12:AT12"/>
     <mergeCell ref="AM48:AP48"/>
     <mergeCell ref="AY47:BB47"/>
     <mergeCell ref="V60:AL60"/>
     <mergeCell ref="AQ72:AT72"/>
+    <mergeCell ref="AY96:BB96"/>
     <mergeCell ref="BC54:BF54"/>
     <mergeCell ref="V45:AL45"/>
     <mergeCell ref="V32:AL32"/>
     <mergeCell ref="V26:AL26"/>
+    <mergeCell ref="BC100:BF100"/>
+    <mergeCell ref="AY98:BB98"/>
     <mergeCell ref="AU70:AX70"/>
     <mergeCell ref="AM73:AP73"/>
     <mergeCell ref="AM70:AP70"/>
@@ -10694,6 +12655,7 @@
     <mergeCell ref="AY16:BB16"/>
     <mergeCell ref="E14:U14"/>
     <mergeCell ref="B87:D87"/>
+    <mergeCell ref="AQ90:AT90"/>
     <mergeCell ref="AM76:AP76"/>
     <mergeCell ref="AY27:BB27"/>
     <mergeCell ref="AQ27:AT27"/>
@@ -10701,27 +12663,38 @@
     <mergeCell ref="AM51:AP51"/>
     <mergeCell ref="AY18:BB18"/>
     <mergeCell ref="AY45:BB45"/>
+    <mergeCell ref="BC105:BF105"/>
     <mergeCell ref="AU58:AX58"/>
+    <mergeCell ref="AY91:BB91"/>
     <mergeCell ref="BC49:BF49"/>
     <mergeCell ref="B51:D51"/>
     <mergeCell ref="AQ25:AT25"/>
     <mergeCell ref="AQ85:AT85"/>
     <mergeCell ref="AY85:BB85"/>
     <mergeCell ref="BC36:BF36"/>
+    <mergeCell ref="AU110:AX110"/>
     <mergeCell ref="AY22:BB22"/>
     <mergeCell ref="AU60:AX60"/>
+    <mergeCell ref="E90:U90"/>
+    <mergeCell ref="BC113:BF113"/>
+    <mergeCell ref="AM92:AP92"/>
+    <mergeCell ref="B113:D113"/>
     <mergeCell ref="E27:U27"/>
     <mergeCell ref="BC50:BF50"/>
     <mergeCell ref="V70:AL70"/>
+    <mergeCell ref="E91:U91"/>
     <mergeCell ref="E25:U25"/>
     <mergeCell ref="AU55:AX55"/>
     <mergeCell ref="E85:U85"/>
     <mergeCell ref="BC39:BF39"/>
     <mergeCell ref="B77:D77"/>
     <mergeCell ref="AM87:AP87"/>
+    <mergeCell ref="AY111:BB111"/>
     <mergeCell ref="AQ38:AT38"/>
     <mergeCell ref="E22:U22"/>
+    <mergeCell ref="V109:AL109"/>
     <mergeCell ref="V47:AL47"/>
+    <mergeCell ref="E93:U93"/>
     <mergeCell ref="AQ13:AT13"/>
     <mergeCell ref="AY48:BB48"/>
     <mergeCell ref="AU7:AX7"/>
@@ -10736,6 +12709,7 @@
     <mergeCell ref="AQ80:AT80"/>
     <mergeCell ref="AU71:AX71"/>
     <mergeCell ref="V48:AL48"/>
+    <mergeCell ref="AM101:AP101"/>
     <mergeCell ref="AU8:AX8"/>
     <mergeCell ref="E38:U38"/>
     <mergeCell ref="V63:AL63"/>
@@ -10743,22 +12717,30 @@
     <mergeCell ref="AU73:AX73"/>
     <mergeCell ref="E13:U13"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B95:D95"/>
     <mergeCell ref="B89:D89"/>
     <mergeCell ref="AU10:AX10"/>
     <mergeCell ref="E40:U40"/>
+    <mergeCell ref="AQ104:AT104"/>
     <mergeCell ref="AY17:BB17"/>
     <mergeCell ref="E15:U15"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="AY66:BB66"/>
+    <mergeCell ref="AQ91:AT91"/>
     <mergeCell ref="AY53:BB53"/>
+    <mergeCell ref="B97:D97"/>
     <mergeCell ref="AM77:AP77"/>
+    <mergeCell ref="E104:U104"/>
+    <mergeCell ref="AQ106:AT106"/>
     <mergeCell ref="BC57:BF57"/>
     <mergeCell ref="AQ33:AT33"/>
     <mergeCell ref="AY68:BB68"/>
+    <mergeCell ref="B90:D90"/>
     <mergeCell ref="AU84:AX84"/>
     <mergeCell ref="AY55:BB55"/>
     <mergeCell ref="V66:AL66"/>
+    <mergeCell ref="AQ105:AT105"/>
     <mergeCell ref="AQ43:AT43"/>
     <mergeCell ref="V53:AL53"/>
     <mergeCell ref="B27:D27"/>
@@ -10766,30 +12748,40 @@
     <mergeCell ref="BC83:BF83"/>
     <mergeCell ref="V22:AL22"/>
     <mergeCell ref="AU86:AX86"/>
+    <mergeCell ref="AY107:BB107"/>
+    <mergeCell ref="V95:AL95"/>
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="BC58:BF58"/>
     <mergeCell ref="BC52:BF52"/>
     <mergeCell ref="AQ28:AT28"/>
+    <mergeCell ref="AU101:AX101"/>
     <mergeCell ref="AM31:AP31"/>
     <mergeCell ref="V61:AL61"/>
+    <mergeCell ref="E106:U106"/>
     <mergeCell ref="B44:D44"/>
     <mergeCell ref="AM3:AP3"/>
     <mergeCell ref="BC60:BF60"/>
+    <mergeCell ref="AM108:AP108"/>
     <mergeCell ref="BC81:BF81"/>
     <mergeCell ref="AU21:AX21"/>
     <mergeCell ref="AQ59:AT59"/>
+    <mergeCell ref="AM95:AP95"/>
     <mergeCell ref="AY46:BB46"/>
     <mergeCell ref="AM89:AP89"/>
     <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B108:D108"/>
     <mergeCell ref="AM32:AP32"/>
     <mergeCell ref="AY12:BB12"/>
     <mergeCell ref="AM26:AP26"/>
     <mergeCell ref="AU23:AX23"/>
+    <mergeCell ref="AM97:AP97"/>
+    <mergeCell ref="E107:U107"/>
     <mergeCell ref="E28:U28"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="AQ54:AT54"/>
     <mergeCell ref="AY41:BB41"/>
     <mergeCell ref="AU79:AX79"/>
+    <mergeCell ref="AY112:BB112"/>
     <mergeCell ref="BC70:BF70"/>
     <mergeCell ref="E30:U30"/>
     <mergeCell ref="AY13:BB13"/>
@@ -10805,16 +12797,21 @@
     <mergeCell ref="E61:U61"/>
     <mergeCell ref="BC71:BF71"/>
     <mergeCell ref="AU74:AX74"/>
+    <mergeCell ref="B96:D96"/>
     <mergeCell ref="E54:U54"/>
     <mergeCell ref="E41:U41"/>
+    <mergeCell ref="E112:U112"/>
     <mergeCell ref="AU76:AX76"/>
+    <mergeCell ref="B111:D111"/>
     <mergeCell ref="AY67:BB67"/>
     <mergeCell ref="AY5:BB5"/>
+    <mergeCell ref="B98:D98"/>
     <mergeCell ref="E56:U56"/>
     <mergeCell ref="B1:BA1"/>
     <mergeCell ref="V3:AL3"/>
     <mergeCell ref="E43:U43"/>
     <mergeCell ref="V68:AL68"/>
+    <mergeCell ref="AQ107:AT107"/>
     <mergeCell ref="AQ34:AT34"/>
     <mergeCell ref="AY69:BB69"/>
     <mergeCell ref="AY25:BB25"/>
@@ -10822,15 +12819,22 @@
     <mergeCell ref="V5:AL5"/>
     <mergeCell ref="AQ49:AT49"/>
     <mergeCell ref="AM85:AP85"/>
+    <mergeCell ref="V97:AL97"/>
     <mergeCell ref="AQ36:AT36"/>
     <mergeCell ref="AQ30:AT30"/>
     <mergeCell ref="V72:AL72"/>
+    <mergeCell ref="AU92:AX92"/>
     <mergeCell ref="V69:AL69"/>
+    <mergeCell ref="V96:AL96"/>
+    <mergeCell ref="BC99:BF99"/>
     <mergeCell ref="AU29:AX29"/>
+    <mergeCell ref="AU94:AX94"/>
     <mergeCell ref="E34:U34"/>
     <mergeCell ref="E9:U9"/>
     <mergeCell ref="B45:D45"/>
+    <mergeCell ref="V98:AL98"/>
     <mergeCell ref="AU44:AX44"/>
+    <mergeCell ref="AM96:AP96"/>
     <mergeCell ref="AU31:AX31"/>
     <mergeCell ref="AU87:AX87"/>
     <mergeCell ref="AY38:BB38"/>
@@ -10838,13 +12842,18 @@
     <mergeCell ref="E11:U11"/>
     <mergeCell ref="E36:U36"/>
     <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B109:D109"/>
+    <mergeCell ref="AM111:AP111"/>
+    <mergeCell ref="AQ112:AT112"/>
     <mergeCell ref="AY62:BB62"/>
     <mergeCell ref="AU24:AX24"/>
     <mergeCell ref="B59:D59"/>
     <mergeCell ref="AQ62:AT62"/>
+    <mergeCell ref="AM98:AP98"/>
     <mergeCell ref="AU89:AX89"/>
     <mergeCell ref="AY24:BB24"/>
     <mergeCell ref="B46:D46"/>
+    <mergeCell ref="E100:U100"/>
     <mergeCell ref="AY28:BB28"/>
     <mergeCell ref="V16:AL16"/>
     <mergeCell ref="AY64:BB64"/>
@@ -10853,17 +12862,20 @@
     <mergeCell ref="AY51:BB51"/>
     <mergeCell ref="B48:D48"/>
     <mergeCell ref="AY82:BB82"/>
+    <mergeCell ref="E102:U102"/>
     <mergeCell ref="V43:AL43"/>
     <mergeCell ref="V18:AL18"/>
     <mergeCell ref="BC8:BF8"/>
     <mergeCell ref="BC79:BF79"/>
     <mergeCell ref="BC73:BF73"/>
     <mergeCell ref="AM16:AP16"/>
+    <mergeCell ref="V91:AL91"/>
     <mergeCell ref="E62:U62"/>
     <mergeCell ref="V85:AL85"/>
     <mergeCell ref="V82:AL82"/>
     <mergeCell ref="BC10:BF10"/>
     <mergeCell ref="AM18:AP18"/>
+    <mergeCell ref="BC102:BF102"/>
     <mergeCell ref="AU42:AX42"/>
     <mergeCell ref="E4:U4"/>
     <mergeCell ref="E64:U64"/>
@@ -10874,46 +12886,61 @@
     <mergeCell ref="AU77:AX77"/>
     <mergeCell ref="AY77:BB77"/>
     <mergeCell ref="AM53:AP53"/>
+    <mergeCell ref="AM109:AP109"/>
     <mergeCell ref="AY33:BB33"/>
     <mergeCell ref="AQ11:AT11"/>
     <mergeCell ref="AM47:AP47"/>
+    <mergeCell ref="BC110:BF110"/>
     <mergeCell ref="AU19:AX19"/>
     <mergeCell ref="AM22:AP22"/>
     <mergeCell ref="AM19:AP19"/>
+    <mergeCell ref="BC103:BF103"/>
     <mergeCell ref="B41:D41"/>
     <mergeCell ref="E65:U65"/>
     <mergeCell ref="AY75:BB75"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="AQ75:AT75"/>
+    <mergeCell ref="AQ100:AT100"/>
     <mergeCell ref="V6:AL6"/>
     <mergeCell ref="AQ50:AT50"/>
+    <mergeCell ref="BC101:BF101"/>
     <mergeCell ref="AM44:AP44"/>
     <mergeCell ref="B66:D66"/>
     <mergeCell ref="V75:AL75"/>
     <mergeCell ref="AQ52:AT52"/>
     <mergeCell ref="AY14:BB14"/>
     <mergeCell ref="AQ39:AT39"/>
+    <mergeCell ref="AU108:AX108"/>
     <mergeCell ref="BC21:BF21"/>
     <mergeCell ref="AY59:BB59"/>
+    <mergeCell ref="BC92:BF92"/>
+    <mergeCell ref="AU95:AX95"/>
     <mergeCell ref="E75:U75"/>
     <mergeCell ref="AU32:AX32"/>
     <mergeCell ref="B67:D67"/>
     <mergeCell ref="E50:U50"/>
     <mergeCell ref="BC23:BF23"/>
     <mergeCell ref="B61:D61"/>
+    <mergeCell ref="AU97:AX97"/>
     <mergeCell ref="AY88:BB88"/>
     <mergeCell ref="E12:U12"/>
+    <mergeCell ref="AU109:AX109"/>
     <mergeCell ref="AM12:AP12"/>
     <mergeCell ref="AU47:AX47"/>
+    <mergeCell ref="AU96:AX96"/>
     <mergeCell ref="AY54:BB54"/>
     <mergeCell ref="E52:U52"/>
     <mergeCell ref="B69:D69"/>
+    <mergeCell ref="AY90:BB90"/>
     <mergeCell ref="E39:U39"/>
+    <mergeCell ref="B112:D112"/>
     <mergeCell ref="AY65:BB65"/>
     <mergeCell ref="AM41:AP41"/>
     <mergeCell ref="V88:AL88"/>
     <mergeCell ref="AQ65:AT65"/>
+    <mergeCell ref="BC98:BF98"/>
     <mergeCell ref="AQ70:AT70"/>
+    <mergeCell ref="E103:U103"/>
     <mergeCell ref="V19:AL19"/>
     <mergeCell ref="B64:D64"/>
     <mergeCell ref="AU63:AX63"/>
@@ -10951,24 +12978,34 @@
     <mergeCell ref="AQ78:AT78"/>
     <mergeCell ref="BC29:BF29"/>
     <mergeCell ref="V14:AL14"/>
+    <mergeCell ref="BC94:BF94"/>
     <mergeCell ref="AM37:AP37"/>
+    <mergeCell ref="V112:AL112"/>
     <mergeCell ref="AY15:BB15"/>
     <mergeCell ref="E83:U83"/>
+    <mergeCell ref="V106:AL106"/>
     <mergeCell ref="BC44:BF44"/>
     <mergeCell ref="AY80:BB80"/>
     <mergeCell ref="V13:AL13"/>
     <mergeCell ref="BC31:BF31"/>
     <mergeCell ref="V78:AL78"/>
+    <mergeCell ref="V105:AL105"/>
     <mergeCell ref="AQ55:AT55"/>
     <mergeCell ref="E20:U20"/>
+    <mergeCell ref="BC108:BF108"/>
+    <mergeCell ref="AU111:AX111"/>
     <mergeCell ref="AU38:AX38"/>
     <mergeCell ref="B6:D6"/>
+    <mergeCell ref="BC95:BF95"/>
     <mergeCell ref="AM38:AP38"/>
+    <mergeCell ref="AU98:AX98"/>
     <mergeCell ref="E84:U84"/>
+    <mergeCell ref="V107:AL107"/>
     <mergeCell ref="AM13:AP13"/>
     <mergeCell ref="AU48:AX48"/>
     <mergeCell ref="E78:U78"/>
     <mergeCell ref="BC32:BF32"/>
+    <mergeCell ref="AM105:AP105"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="AQ7:AT7"/>
     <mergeCell ref="AY4:BB4"/>
@@ -10982,6 +13019,10 @@
     <mergeCell ref="V27:AL27"/>
     <mergeCell ref="AQ71:AT71"/>
     <mergeCell ref="B72:D72"/>
+    <mergeCell ref="AY106:BB106"/>
+    <mergeCell ref="AM107:AP107"/>
+    <mergeCell ref="AY93:BB93"/>
+    <mergeCell ref="V104:AL104"/>
     <mergeCell ref="AM57:AP57"/>
     <mergeCell ref="V25:AL25"/>
     <mergeCell ref="AQ8:AT8"/>
@@ -11013,13 +13054,18 @@
     <mergeCell ref="E10:U10"/>
     <mergeCell ref="B83:D83"/>
     <mergeCell ref="AQ86:AT86"/>
+    <mergeCell ref="AU107:AX107"/>
+    <mergeCell ref="AM110:AP110"/>
     <mergeCell ref="V84:AL84"/>
     <mergeCell ref="V59:AL59"/>
+    <mergeCell ref="AY104:BB104"/>
     <mergeCell ref="AM72:AP72"/>
     <mergeCell ref="BC85:BF85"/>
     <mergeCell ref="AM28:AP28"/>
+    <mergeCell ref="AQ101:AT101"/>
     <mergeCell ref="V40:AL40"/>
     <mergeCell ref="E74:U74"/>
+    <mergeCell ref="B110:D110"/>
     <mergeCell ref="B85:D85"/>
     <mergeCell ref="V15:AL15"/>
     <mergeCell ref="V51:AL51"/>
@@ -11029,15 +13075,18 @@
     <mergeCell ref="AM59:AP59"/>
     <mergeCell ref="BC53:BF53"/>
     <mergeCell ref="BC47:BF47"/>
+    <mergeCell ref="BC96:BF96"/>
     <mergeCell ref="AM88:AP88"/>
     <mergeCell ref="AM82:AP82"/>
     <mergeCell ref="AU54:AX54"/>
+    <mergeCell ref="BC111:BF111"/>
     <mergeCell ref="AM54:AP54"/>
     <mergeCell ref="AU41:AX41"/>
     <mergeCell ref="AU16:AX16"/>
     <mergeCell ref="BC76:BF76"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="AQ79:AT79"/>
+    <mergeCell ref="AM90:AP90"/>
     <mergeCell ref="E21:U21"/>
     <mergeCell ref="BC48:BF48"/>
     <mergeCell ref="AQ35:AT35"/>
@@ -11050,34 +13099,54 @@
     <mergeCell ref="AU43:AX43"/>
     <mergeCell ref="AY34:BB34"/>
     <mergeCell ref="B78:D78"/>
+    <mergeCell ref="AY105:BB105"/>
     <mergeCell ref="BC63:BF63"/>
+    <mergeCell ref="AY99:BB99"/>
     <mergeCell ref="E23:U23"/>
+    <mergeCell ref="AQ99:AT99"/>
     <mergeCell ref="V35:AL35"/>
     <mergeCell ref="AQ74:AT74"/>
     <mergeCell ref="AY36:BB36"/>
+    <mergeCell ref="AQ110:AT110"/>
     <mergeCell ref="E87:U87"/>
+    <mergeCell ref="AY101:BB101"/>
     <mergeCell ref="V34:AL34"/>
     <mergeCell ref="AQ89:AT89"/>
     <mergeCell ref="V28:AL28"/>
+    <mergeCell ref="V99:AL99"/>
     <mergeCell ref="AQ76:AT76"/>
     <mergeCell ref="AU67:AX67"/>
+    <mergeCell ref="AY100:BB100"/>
     <mergeCell ref="AU5:AX5"/>
+    <mergeCell ref="AQ103:AT103"/>
     <mergeCell ref="V30:AL30"/>
+    <mergeCell ref="E105:U105"/>
     <mergeCell ref="AU9:AX9"/>
     <mergeCell ref="AM34:AP34"/>
     <mergeCell ref="AU69:AX69"/>
+    <mergeCell ref="E99:U99"/>
+    <mergeCell ref="B91:D91"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="E49:U49"/>
+    <mergeCell ref="E110:U110"/>
     <mergeCell ref="BC22:BF22"/>
+    <mergeCell ref="E101:U101"/>
     <mergeCell ref="B22:D22"/>
+    <mergeCell ref="AQ92:AT92"/>
     <mergeCell ref="E76:U76"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="E113:U113"/>
     <mergeCell ref="AM78:AP78"/>
+    <mergeCell ref="AQ102:AT102"/>
+    <mergeCell ref="V90:AL90"/>
     <mergeCell ref="AQ29:AT29"/>
     <mergeCell ref="B86:D86"/>
     <mergeCell ref="AQ23:AT23"/>
     <mergeCell ref="V65:AL65"/>
+    <mergeCell ref="AQ94:AT94"/>
     <mergeCell ref="V62:AL62"/>
     <mergeCell ref="V56:AL56"/>
+    <mergeCell ref="B101:D101"/>
     <mergeCell ref="BC55:BF55"/>
     <mergeCell ref="AQ31:AT31"/>
     <mergeCell ref="AQ87:AT87"/>
@@ -11092,16 +13161,24 @@
     <mergeCell ref="AQ26:AT26"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="AU51:AX51"/>
+    <mergeCell ref="AM91:AP91"/>
     <mergeCell ref="AU82:AX82"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="E31:U31"/>
+    <mergeCell ref="B104:D104"/>
     <mergeCell ref="V9:AL9"/>
     <mergeCell ref="AY8:BB8"/>
     <mergeCell ref="BC41:BF41"/>
     <mergeCell ref="AY57:BB57"/>
     <mergeCell ref="AQ57:AT57"/>
     <mergeCell ref="B79:D79"/>
+    <mergeCell ref="AM93:AP93"/>
+    <mergeCell ref="E108:U108"/>
+    <mergeCell ref="AQ113:AT113"/>
+    <mergeCell ref="AY113:BB113"/>
     <mergeCell ref="V49:AL49"/>
+    <mergeCell ref="E95:U95"/>
+    <mergeCell ref="B106:D106"/>
     <mergeCell ref="E89:U89"/>
     <mergeCell ref="AY50:BB50"/>
     <mergeCell ref="V36:AL36"/>
@@ -11111,6 +13188,9 @@
     <mergeCell ref="AM9:AP9"/>
     <mergeCell ref="AQ42:AT42"/>
     <mergeCell ref="E26:U26"/>
+    <mergeCell ref="AY102:BB102"/>
+    <mergeCell ref="V113:AL113"/>
+    <mergeCell ref="AM103:AP103"/>
     <mergeCell ref="AY52:BB52"/>
     <mergeCell ref="AQ77:AT77"/>
     <mergeCell ref="AY39:BB39"/>
@@ -11122,8 +13202,10 @@
     <mergeCell ref="BC67:BF67"/>
     <mergeCell ref="AM84:AP84"/>
     <mergeCell ref="BC5:BF5"/>
+    <mergeCell ref="AY103:BB103"/>
     <mergeCell ref="AM4:AP4"/>
     <mergeCell ref="AM75:AP75"/>
+    <mergeCell ref="BC97:BF97"/>
     <mergeCell ref="AQ4:AT4"/>
     <mergeCell ref="AU37:AX37"/>
     <mergeCell ref="AM50:AP50"/>
@@ -11137,21 +13219,32 @@
     <mergeCell ref="AM86:AP86"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B28:D28"/>
+    <mergeCell ref="AM104:AP104"/>
     <mergeCell ref="V4:AL4"/>
     <mergeCell ref="AM79:AP79"/>
     <mergeCell ref="V64:AL64"/>
     <mergeCell ref="E44:U44"/>
+    <mergeCell ref="AQ108:AT108"/>
     <mergeCell ref="AY21:BB21"/>
     <mergeCell ref="AY70:BB70"/>
+    <mergeCell ref="B92:D92"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="AQ95:AT95"/>
+    <mergeCell ref="AM106:AP106"/>
     <mergeCell ref="AQ45:AT45"/>
     <mergeCell ref="AM81:AP81"/>
+    <mergeCell ref="V93:AL93"/>
     <mergeCell ref="AQ32:AT32"/>
     <mergeCell ref="AY23:BB23"/>
+    <mergeCell ref="B94:D94"/>
+    <mergeCell ref="AQ97:AT97"/>
     <mergeCell ref="AU88:AX88"/>
+    <mergeCell ref="AQ109:AT109"/>
     <mergeCell ref="AQ47:AT47"/>
+    <mergeCell ref="AQ96:AT96"/>
     <mergeCell ref="BC16:BF16"/>
     <mergeCell ref="B54:D54"/>
+    <mergeCell ref="AU90:AX90"/>
     <mergeCell ref="BC62:BF62"/>
     <mergeCell ref="AU65:AX65"/>
     <mergeCell ref="E70:U70"/>
@@ -11163,16 +13256,26 @@
     <mergeCell ref="B56:D56"/>
     <mergeCell ref="AY83:BB83"/>
     <mergeCell ref="E32:U32"/>
+    <mergeCell ref="B105:D105"/>
     <mergeCell ref="B43:D43"/>
+    <mergeCell ref="E97:U97"/>
     <mergeCell ref="AM63:AP63"/>
     <mergeCell ref="AU25:AX25"/>
+    <mergeCell ref="E109:U109"/>
     <mergeCell ref="AQ63:AT63"/>
     <mergeCell ref="E47:U47"/>
     <mergeCell ref="AU85:AX85"/>
+    <mergeCell ref="AM99:AP99"/>
+    <mergeCell ref="E96:U96"/>
+    <mergeCell ref="AY110:BB110"/>
+    <mergeCell ref="B107:D107"/>
     <mergeCell ref="V86:AL86"/>
     <mergeCell ref="AY60:BB60"/>
+    <mergeCell ref="E111:U111"/>
     <mergeCell ref="V58:AL58"/>
     <mergeCell ref="V52:AL52"/>
+    <mergeCell ref="E98:U98"/>
+    <mergeCell ref="AM94:AP94"/>
     <mergeCell ref="BC9:BF9"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="V81:AL81"/>
@@ -11185,6 +13288,7 @@
     <mergeCell ref="AM14:AP14"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="E60:U60"/>
+    <mergeCell ref="AM112:AP112"/>
     <mergeCell ref="AQ22:AT22"/>
     <mergeCell ref="X2:BB2"/>
     <mergeCell ref="AU13:AX13"/>
@@ -11193,40 +13297,55 @@
     <mergeCell ref="AM56:AP56"/>
     <mergeCell ref="BC75:BF75"/>
     <mergeCell ref="AU78:AX78"/>
+    <mergeCell ref="B100:D100"/>
     <mergeCell ref="B75:D75"/>
     <mergeCell ref="AU15:AX15"/>
     <mergeCell ref="E45:U45"/>
     <mergeCell ref="AU80:AX80"/>
     <mergeCell ref="AY71:BB71"/>
     <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B102:D102"/>
     <mergeCell ref="AY58:BB58"/>
     <mergeCell ref="V7:AL7"/>
     <mergeCell ref="BC87:BF87"/>
+    <mergeCell ref="AQ111:AT111"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="AY73:BB73"/>
     <mergeCell ref="BC24:BF24"/>
     <mergeCell ref="V71:AL71"/>
     <mergeCell ref="AQ48:AT48"/>
     <mergeCell ref="AY10:BB10"/>
+    <mergeCell ref="V101:AL101"/>
+    <mergeCell ref="AU104:AX104"/>
     <mergeCell ref="AM7:AP7"/>
     <mergeCell ref="BC88:BF88"/>
+    <mergeCell ref="AU91:AX91"/>
     <mergeCell ref="BC82:BF82"/>
     <mergeCell ref="AM25:AP25"/>
     <mergeCell ref="V73:AL73"/>
+    <mergeCell ref="V100:AL100"/>
     <mergeCell ref="E71:U71"/>
+    <mergeCell ref="AU106:AX106"/>
+    <mergeCell ref="BC93:BF93"/>
     <mergeCell ref="AU33:AX33"/>
     <mergeCell ref="AM36:AP36"/>
+    <mergeCell ref="BC90:BF90"/>
     <mergeCell ref="AM33:AP33"/>
+    <mergeCell ref="AU93:AX93"/>
+    <mergeCell ref="V102:AL102"/>
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="AM8:AP8"/>
     <mergeCell ref="BC65:BF65"/>
     <mergeCell ref="E73:U73"/>
     <mergeCell ref="V20:AL20"/>
+    <mergeCell ref="AM113:AP113"/>
     <mergeCell ref="V77:AL77"/>
     <mergeCell ref="B65:D65"/>
+    <mergeCell ref="AM100:AP100"/>
     <mergeCell ref="AU28:AX28"/>
     <mergeCell ref="B63:D63"/>
     <mergeCell ref="AQ66:AT66"/>
+    <mergeCell ref="AM102:AP102"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="AQ53:AT53"/>
     <mergeCell ref="AQ3:AT3"/>
@@ -11245,6 +13364,7 @@
     <mergeCell ref="E53:U53"/>
     <mergeCell ref="BC14:BF14"/>
     <mergeCell ref="AY79:BB79"/>
+    <mergeCell ref="BC112:BF112"/>
     <mergeCell ref="E68:U68"/>
     <mergeCell ref="BC13:BF13"/>
     <mergeCell ref="E55:U55"/>
@@ -11252,11 +13372,13 @@
     <mergeCell ref="AM21:AP21"/>
     <mergeCell ref="AU81:AX81"/>
     <mergeCell ref="E67:U67"/>
+    <mergeCell ref="B103:D103"/>
     <mergeCell ref="E5:U5"/>
     <mergeCell ref="V8:AL8"/>
     <mergeCell ref="V79:AL79"/>
     <mergeCell ref="E48:U48"/>
     <mergeCell ref="AY74:BB74"/>
+    <mergeCell ref="BC107:BF107"/>
     <mergeCell ref="V10:AL10"/>
     <mergeCell ref="B55:D55"/>
     <mergeCell ref="AQ41:AT41"/>
@@ -11267,17 +13389,25 @@
     <mergeCell ref="AU35:AX35"/>
     <mergeCell ref="AQ51:AT51"/>
     <mergeCell ref="V39:AL39"/>
+    <mergeCell ref="V110:AL110"/>
+    <mergeCell ref="BC104:BF104"/>
     <mergeCell ref="AU34:AX34"/>
+    <mergeCell ref="BC91:BF91"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="BC25:BF25"/>
     <mergeCell ref="AY63:BB63"/>
+    <mergeCell ref="AU99:AX99"/>
+    <mergeCell ref="AU105:AX105"/>
+    <mergeCell ref="V103:AL103"/>
     <mergeCell ref="AU49:AX49"/>
     <mergeCell ref="AM52:AP52"/>
+    <mergeCell ref="BC106:BF106"/>
     <mergeCell ref="AM49:AP49"/>
     <mergeCell ref="AU36:AX36"/>
     <mergeCell ref="AM39:AP39"/>
     <mergeCell ref="B71:D71"/>
     <mergeCell ref="B58:D58"/>
+    <mergeCell ref="AY92:BB92"/>
     <mergeCell ref="E16:U16"/>
     <mergeCell ref="B52:D52"/>
     <mergeCell ref="AQ67:AT67"/>
